--- a/research/traditional_assets/database/data/oman/oman_shipbuilding_marine.xlsx
+++ b/research/traditional_assets/database/data/oman/oman_shipbuilding_marine.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1117432886994339</v>
+        <v>0.1116139237663847</v>
       </c>
       <c r="C2">
-        <v>196.9195097718139</v>
+        <v>195.3151080718182</v>
       </c>
       <c r="D2">
-        <v>152.4195097718139</v>
+        <v>152.7191080718182</v>
       </c>
       <c r="E2">
-        <v>-59.6</v>
+        <v>-57.696</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.904</v>
       </c>
       <c r="G2">
         <v>44.5</v>
@@ -1451,28 +1451,28 @@
         <v>36.438</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0957712</v>
       </c>
       <c r="N2">
-        <v>36.438</v>
+        <v>36.3422288</v>
       </c>
       <c r="O2">
-        <v>5.4657</v>
+        <v>5.45133432</v>
       </c>
       <c r="P2">
-        <v>30.9723</v>
+        <v>30.89089448</v>
       </c>
       <c r="Q2">
-        <v>31.40930000000001</v>
+        <v>31.32789448</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1117432886994339</v>
+        <v>0.1123094684508937</v>
       </c>
       <c r="T2">
-        <v>0.8594621135367392</v>
+        <v>0.8668413337034686</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>380.4692851295588</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1116139237663847</v>
+        <v>0.1114845588333356</v>
       </c>
       <c r="C3">
-        <v>195.3151080718182</v>
+        <v>193.7118864821774</v>
       </c>
       <c r="D3">
-        <v>152.7191080718182</v>
+        <v>153.0198864821774</v>
       </c>
       <c r="E3">
-        <v>-57.696</v>
+        <v>-55.792</v>
       </c>
       <c r="F3">
-        <v>1.904</v>
+        <v>3.808</v>
       </c>
       <c r="G3">
         <v>44.5</v>
@@ -1533,28 +1533,28 @@
         <v>36.438</v>
       </c>
       <c r="M3">
-        <v>0.0957712</v>
+        <v>0.1915424</v>
       </c>
       <c r="N3">
-        <v>36.3422288</v>
+        <v>36.2464576</v>
       </c>
       <c r="O3">
-        <v>5.45133432</v>
+        <v>5.43696864</v>
       </c>
       <c r="P3">
-        <v>30.89089448</v>
+        <v>30.80948896</v>
       </c>
       <c r="Q3">
-        <v>31.32789448</v>
+        <v>31.24648896</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1123094684508937</v>
+        <v>0.1128872028911588</v>
       </c>
       <c r="T3">
-        <v>0.8668413337034686</v>
+        <v>0.8743711502001317</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>380.4692851295588</v>
+        <v>190.2346425647794</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1114845588333356</v>
+        <v>0.1113551939002864</v>
       </c>
       <c r="C4">
-        <v>193.7118864821774</v>
+        <v>192.1098519892898</v>
       </c>
       <c r="D4">
-        <v>153.0198864821774</v>
+        <v>153.3218519892898</v>
       </c>
       <c r="E4">
-        <v>-55.792</v>
+        <v>-53.88800000000001</v>
       </c>
       <c r="F4">
-        <v>3.808</v>
+        <v>5.712</v>
       </c>
       <c r="G4">
         <v>44.5</v>
@@ -1615,28 +1615,28 @@
         <v>36.438</v>
       </c>
       <c r="M4">
-        <v>0.1915424</v>
+        <v>0.2873135999999999</v>
       </c>
       <c r="N4">
-        <v>36.2464576</v>
+        <v>36.1506864</v>
       </c>
       <c r="O4">
-        <v>5.43696864</v>
+        <v>5.422602960000001</v>
       </c>
       <c r="P4">
-        <v>30.80948896</v>
+        <v>30.72808344000001</v>
       </c>
       <c r="Q4">
-        <v>31.24648896</v>
+        <v>31.16508344000001</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1128872028911588</v>
+        <v>0.1134768493817386</v>
       </c>
       <c r="T4">
-        <v>0.8743711502001317</v>
+        <v>0.8820562206451792</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>190.2346425647794</v>
+        <v>126.8230950431863</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1113551939002864</v>
+        <v>0.1112258289672373</v>
       </c>
       <c r="C5">
-        <v>192.1098519892898</v>
+        <v>190.5090116348099</v>
       </c>
       <c r="D5">
-        <v>153.3218519892898</v>
+        <v>153.6250116348099</v>
       </c>
       <c r="E5">
-        <v>-53.88800000000001</v>
+        <v>-51.984</v>
       </c>
       <c r="F5">
-        <v>5.712</v>
+        <v>7.616000000000001</v>
       </c>
       <c r="G5">
         <v>44.5</v>
@@ -1697,28 +1697,28 @@
         <v>36.438</v>
       </c>
       <c r="M5">
-        <v>0.2873135999999999</v>
+        <v>0.3830848</v>
       </c>
       <c r="N5">
-        <v>36.1506864</v>
+        <v>36.0549152</v>
       </c>
       <c r="O5">
-        <v>5.422602960000001</v>
+        <v>5.408237280000001</v>
       </c>
       <c r="P5">
-        <v>30.72808344000001</v>
+        <v>30.64667792</v>
       </c>
       <c r="Q5">
-        <v>31.16508344000001</v>
+        <v>31.08367792</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1134768493817386</v>
+        <v>0.1140787801742055</v>
       </c>
       <c r="T5">
-        <v>0.8820562206451792</v>
+        <v>0.8899013967244986</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>126.8230950431863</v>
+        <v>95.11732128238971</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1112258289672373</v>
+        <v>0.1110964640341881</v>
       </c>
       <c r="C6">
-        <v>190.5090116348099</v>
+        <v>188.9093725161956</v>
       </c>
       <c r="D6">
-        <v>153.6250116348099</v>
+        <v>153.9293725161956</v>
       </c>
       <c r="E6">
-        <v>-51.984</v>
+        <v>-50.08</v>
       </c>
       <c r="F6">
-        <v>7.616000000000001</v>
+        <v>9.520000000000001</v>
       </c>
       <c r="G6">
         <v>44.5</v>
@@ -1779,28 +1779,28 @@
         <v>36.438</v>
       </c>
       <c r="M6">
-        <v>0.3830848</v>
+        <v>0.4788560000000001</v>
       </c>
       <c r="N6">
-        <v>36.0549152</v>
+        <v>35.959144</v>
       </c>
       <c r="O6">
-        <v>5.408237280000001</v>
+        <v>5.3938716</v>
       </c>
       <c r="P6">
-        <v>30.64667792</v>
+        <v>30.5652724</v>
       </c>
       <c r="Q6">
-        <v>31.08367792</v>
+        <v>31.0022724</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1140787801742055</v>
+        <v>0.1146933831938823</v>
       </c>
       <c r="T6">
-        <v>0.8899013967244986</v>
+        <v>0.8979117344054881</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>95.11732128238971</v>
+        <v>76.09385702591175</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1110964640341881</v>
+        <v>0.110967099101139</v>
       </c>
       <c r="C7">
-        <v>188.9093725161956</v>
+        <v>187.3109417872622</v>
       </c>
       <c r="D7">
-        <v>153.9293725161956</v>
+        <v>154.2349417872622</v>
       </c>
       <c r="E7">
-        <v>-50.08</v>
+        <v>-48.176</v>
       </c>
       <c r="F7">
-        <v>9.520000000000001</v>
+        <v>11.424</v>
       </c>
       <c r="G7">
         <v>44.5</v>
@@ -1861,28 +1861,28 @@
         <v>36.438</v>
       </c>
       <c r="M7">
-        <v>0.4788560000000001</v>
+        <v>0.5746272</v>
       </c>
       <c r="N7">
-        <v>35.959144</v>
+        <v>35.8633728</v>
       </c>
       <c r="O7">
-        <v>5.3938716</v>
+        <v>5.37950592</v>
       </c>
       <c r="P7">
-        <v>30.5652724</v>
+        <v>30.48386688</v>
       </c>
       <c r="Q7">
-        <v>31.0022724</v>
+        <v>30.92086688</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1146933831938823</v>
+        <v>0.1153210628735521</v>
       </c>
       <c r="T7">
-        <v>0.8979117344054881</v>
+        <v>0.9060925048030941</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>76.09385702591175</v>
+        <v>63.41154752159313</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.110967099101139</v>
+        <v>0.1108377341680899</v>
       </c>
       <c r="C8">
-        <v>187.3109417872622</v>
+        <v>185.7137266587427</v>
       </c>
       <c r="D8">
-        <v>154.2349417872622</v>
+        <v>154.5417266587427</v>
       </c>
       <c r="E8">
-        <v>-48.176</v>
+        <v>-46.27200000000001</v>
       </c>
       <c r="F8">
-        <v>11.424</v>
+        <v>13.328</v>
       </c>
       <c r="G8">
         <v>44.5</v>
@@ -1943,28 +1943,28 @@
         <v>36.438</v>
       </c>
       <c r="M8">
-        <v>0.5746271999999999</v>
+        <v>0.6703983999999999</v>
       </c>
       <c r="N8">
-        <v>35.8633728</v>
+        <v>35.7676016</v>
       </c>
       <c r="O8">
-        <v>5.37950592</v>
+        <v>5.36514024</v>
       </c>
       <c r="P8">
-        <v>30.48386688</v>
+        <v>30.40246136</v>
       </c>
       <c r="Q8">
-        <v>30.92086688</v>
+        <v>30.83946136</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1153210628735521</v>
+        <v>0.1159622410409568</v>
       </c>
       <c r="T8">
-        <v>0.9060925048030941</v>
+        <v>0.9144492057468854</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>63.41154752159314</v>
+        <v>54.3527550185084</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1108377341680898</v>
+        <v>0.1107083692350407</v>
       </c>
       <c r="C9">
-        <v>185.7137266587427</v>
+        <v>184.1177343988558</v>
       </c>
       <c r="D9">
-        <v>154.5417266587427</v>
+        <v>154.8497343988558</v>
       </c>
       <c r="E9">
-        <v>-46.272</v>
+        <v>-44.368</v>
       </c>
       <c r="F9">
-        <v>13.328</v>
+        <v>15.232</v>
       </c>
       <c r="G9">
         <v>44.5</v>
@@ -2025,28 +2025,28 @@
         <v>36.438</v>
       </c>
       <c r="M9">
-        <v>0.6703984000000001</v>
+        <v>0.7661696</v>
       </c>
       <c r="N9">
-        <v>35.7676016</v>
+        <v>35.6718304</v>
       </c>
       <c r="O9">
-        <v>5.36514024</v>
+        <v>5.350774560000001</v>
       </c>
       <c r="P9">
-        <v>30.40246136</v>
+        <v>30.32105584</v>
       </c>
       <c r="Q9">
-        <v>30.83946136</v>
+        <v>30.75805584</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1159622410409568</v>
+        <v>0.1166173578641747</v>
       </c>
       <c r="T9">
-        <v>0.9144492057468854</v>
+        <v>0.9229875741024982</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>54.35275501850839</v>
+        <v>47.55866064119486</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1107083692350407</v>
+        <v>0.1105790043019915</v>
       </c>
       <c r="C10">
-        <v>184.1177343988558</v>
+        <v>182.5229723338787</v>
       </c>
       <c r="D10">
-        <v>154.8497343988558</v>
+        <v>155.1589723338787</v>
       </c>
       <c r="E10">
-        <v>-44.368</v>
+        <v>-42.464</v>
       </c>
       <c r="F10">
-        <v>15.232</v>
+        <v>17.136</v>
       </c>
       <c r="G10">
         <v>44.5</v>
@@ -2107,28 +2107,28 @@
         <v>36.438</v>
       </c>
       <c r="M10">
-        <v>0.7661696</v>
+        <v>0.8619408</v>
       </c>
       <c r="N10">
-        <v>35.6718304</v>
+        <v>35.5760592</v>
       </c>
       <c r="O10">
-        <v>5.350774560000001</v>
+        <v>5.33640888</v>
       </c>
       <c r="P10">
-        <v>30.32105584</v>
+        <v>30.23965032</v>
       </c>
       <c r="Q10">
-        <v>30.75805584</v>
+        <v>30.67665032</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1166173578641747</v>
+        <v>0.1172868728593313</v>
       </c>
       <c r="T10">
-        <v>0.9229875741024982</v>
+        <v>0.931713598905487</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>47.55866064119486</v>
+        <v>42.27436501439543</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1105790043019915</v>
+        <v>0.1104496393689424</v>
       </c>
       <c r="C11">
-        <v>182.5229723338787</v>
+        <v>180.9294478487288</v>
       </c>
       <c r="D11">
-        <v>155.1589723338787</v>
+        <v>155.4694478487287</v>
       </c>
       <c r="E11">
-        <v>-42.464</v>
+        <v>-40.56</v>
       </c>
       <c r="F11">
-        <v>17.136</v>
+        <v>19.04</v>
       </c>
       <c r="G11">
         <v>44.5</v>
@@ -2189,28 +2189,28 @@
         <v>36.438</v>
       </c>
       <c r="M11">
-        <v>0.8619408</v>
+        <v>0.9577119999999999</v>
       </c>
       <c r="N11">
-        <v>35.5760592</v>
+        <v>35.480288</v>
       </c>
       <c r="O11">
-        <v>5.33640888</v>
+        <v>5.3220432</v>
       </c>
       <c r="P11">
-        <v>30.23965032</v>
+        <v>30.1582448</v>
       </c>
       <c r="Q11">
-        <v>30.67665032</v>
+        <v>30.5952448</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1172868728593313</v>
+        <v>0.1179712659654915</v>
       </c>
       <c r="T11">
-        <v>0.931713598905487</v>
+        <v>0.9406335353707647</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>42.27436501439543</v>
+        <v>38.04692851295589</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1104496393689424</v>
+        <v>0.1103202744358932</v>
       </c>
       <c r="C12">
-        <v>180.9294478487288</v>
+        <v>179.3371683875514</v>
       </c>
       <c r="D12">
-        <v>155.4694478487287</v>
+        <v>155.7811683875514</v>
       </c>
       <c r="E12">
-        <v>-40.56</v>
+        <v>-38.65600000000001</v>
       </c>
       <c r="F12">
-        <v>19.04</v>
+        <v>20.944</v>
       </c>
       <c r="G12">
         <v>44.5</v>
@@ -2271,28 +2271,28 @@
         <v>36.438</v>
       </c>
       <c r="M12">
-        <v>0.9577120000000001</v>
+        <v>1.0534832</v>
       </c>
       <c r="N12">
-        <v>35.480288</v>
+        <v>35.3845168</v>
       </c>
       <c r="O12">
-        <v>5.3220432</v>
+        <v>5.307677519999999</v>
       </c>
       <c r="P12">
-        <v>30.1582448</v>
+        <v>30.07683928</v>
       </c>
       <c r="Q12">
-        <v>30.5952448</v>
+        <v>30.51383928</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1179712659654915</v>
+        <v>0.1186710386920149</v>
       </c>
       <c r="T12">
-        <v>0.9406335353707647</v>
+        <v>0.9497539198464977</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>38.04692851295587</v>
+        <v>34.58811682995989</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1103202744358932</v>
+        <v>0.1101909095028441</v>
       </c>
       <c r="C13">
-        <v>179.3371683875514</v>
+        <v>177.7461414543146</v>
       </c>
       <c r="D13">
-        <v>155.7811683875514</v>
+        <v>156.0941414543146</v>
       </c>
       <c r="E13">
-        <v>-38.65600000000001</v>
+        <v>-36.752</v>
       </c>
       <c r="F13">
-        <v>20.944</v>
+        <v>22.848</v>
       </c>
       <c r="G13">
         <v>44.5</v>
@@ -2353,28 +2353,28 @@
         <v>36.438</v>
       </c>
       <c r="M13">
-        <v>1.0534832</v>
+        <v>1.1492544</v>
       </c>
       <c r="N13">
-        <v>35.3845168</v>
+        <v>35.28874560000001</v>
       </c>
       <c r="O13">
-        <v>5.307677519999999</v>
+        <v>5.29331184</v>
       </c>
       <c r="P13">
-        <v>30.07683928</v>
+        <v>29.99543376</v>
       </c>
       <c r="Q13">
-        <v>30.51383928</v>
+        <v>30.43243376000001</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1186710386920149</v>
+        <v>0.119386715344141</v>
       </c>
       <c r="T13">
-        <v>0.9497539198464977</v>
+        <v>0.9590815857875885</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>34.58811682995989</v>
+        <v>31.70577376079657</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1101909095028441</v>
+        <v>0.1100615445697949</v>
       </c>
       <c r="C14">
-        <v>177.7461414543146</v>
+        <v>176.1563746134113</v>
       </c>
       <c r="D14">
-        <v>156.0941414543146</v>
+        <v>156.4083746134113</v>
       </c>
       <c r="E14">
-        <v>-36.752</v>
+        <v>-34.848</v>
       </c>
       <c r="F14">
-        <v>22.848</v>
+        <v>24.752</v>
       </c>
       <c r="G14">
         <v>44.5</v>
@@ -2435,28 +2435,28 @@
         <v>36.438</v>
       </c>
       <c r="M14">
-        <v>1.1492544</v>
+        <v>1.2450256</v>
       </c>
       <c r="N14">
-        <v>35.28874560000001</v>
+        <v>35.1929744</v>
       </c>
       <c r="O14">
-        <v>5.29331184</v>
+        <v>5.27894616</v>
       </c>
       <c r="P14">
-        <v>29.99543376</v>
+        <v>29.91402824</v>
       </c>
       <c r="Q14">
-        <v>30.43243376000001</v>
+        <v>30.35102824000001</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.119386715344141</v>
+        <v>0.1201188443330976</v>
       </c>
       <c r="T14">
-        <v>0.9590815857875885</v>
+        <v>0.9686236808307732</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>31.70577376079657</v>
+        <v>29.26686808688914</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1100615445697949</v>
+        <v>0.1099321796367458</v>
       </c>
       <c r="C15">
-        <v>176.1563746134113</v>
+        <v>174.5678754902691</v>
       </c>
       <c r="D15">
-        <v>156.4083746134113</v>
+        <v>156.7238754902691</v>
       </c>
       <c r="E15">
-        <v>-34.848</v>
+        <v>-32.944</v>
       </c>
       <c r="F15">
-        <v>24.752</v>
+        <v>26.656</v>
       </c>
       <c r="G15">
         <v>44.5</v>
@@ -2517,28 +2517,28 @@
         <v>36.438</v>
       </c>
       <c r="M15">
-        <v>1.2450256</v>
+        <v>1.3407968</v>
       </c>
       <c r="N15">
-        <v>35.1929744</v>
+        <v>35.0972032</v>
       </c>
       <c r="O15">
-        <v>5.27894616</v>
+        <v>5.26458048</v>
       </c>
       <c r="P15">
-        <v>29.91402824</v>
+        <v>29.83262272</v>
       </c>
       <c r="Q15">
-        <v>30.35102824000001</v>
+        <v>30.26962272</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1201188443330976</v>
+        <v>0.1208679995776114</v>
       </c>
       <c r="T15">
-        <v>0.9686236808307732</v>
+        <v>0.9783876850610088</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>29.26686808688914</v>
+        <v>27.1763775092542</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1099321796367458</v>
+        <v>0.1098028147036966</v>
       </c>
       <c r="C16">
-        <v>174.5678754902691</v>
+        <v>172.9806517719664</v>
       </c>
       <c r="D16">
-        <v>156.7238754902691</v>
+        <v>157.0406517719664</v>
       </c>
       <c r="E16">
-        <v>-32.944</v>
+        <v>-31.04</v>
       </c>
       <c r="F16">
-        <v>26.656</v>
+        <v>28.56000000000001</v>
       </c>
       <c r="G16">
         <v>44.5</v>
@@ -2599,28 +2599,28 @@
         <v>36.438</v>
       </c>
       <c r="M16">
-        <v>1.3407968</v>
+        <v>1.436568</v>
       </c>
       <c r="N16">
-        <v>35.0972032</v>
+        <v>35.001432</v>
       </c>
       <c r="O16">
-        <v>5.26458048</v>
+        <v>5.2502148</v>
       </c>
       <c r="P16">
-        <v>29.83262272</v>
+        <v>29.7512172</v>
       </c>
       <c r="Q16">
-        <v>30.26962272</v>
+        <v>30.1882172</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1208679995776114</v>
+        <v>0.121634782004349</v>
       </c>
       <c r="T16">
-        <v>0.9783876850610088</v>
+        <v>0.98838143056725</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>27.1763775092542</v>
+        <v>25.36461900863725</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1098028147036966</v>
+        <v>0.1096734497706475</v>
       </c>
       <c r="C17">
-        <v>172.9806517719664</v>
+        <v>171.3947112078576</v>
       </c>
       <c r="D17">
-        <v>157.0406517719664</v>
+        <v>157.3587112078576</v>
       </c>
       <c r="E17">
-        <v>-31.04</v>
+        <v>-29.136</v>
       </c>
       <c r="F17">
-        <v>28.56</v>
+        <v>30.464</v>
       </c>
       <c r="G17">
         <v>44.5</v>
@@ -2681,28 +2681,28 @@
         <v>36.438</v>
       </c>
       <c r="M17">
-        <v>1.436568</v>
+        <v>1.5323392</v>
       </c>
       <c r="N17">
-        <v>35.001432</v>
+        <v>34.9056608</v>
       </c>
       <c r="O17">
-        <v>5.2502148</v>
+        <v>5.23584912</v>
       </c>
       <c r="P17">
-        <v>29.7512172</v>
+        <v>29.66981168</v>
       </c>
       <c r="Q17">
-        <v>30.1882172</v>
+        <v>30.10681168</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.121634782004349</v>
+        <v>0.1224198211555327</v>
       </c>
       <c r="T17">
-        <v>0.98838143056725</v>
+        <v>0.9986131223950685</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>25.36461900863726</v>
+        <v>23.77933032059742</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1096734497706475</v>
+        <v>0.1095440848375983</v>
       </c>
       <c r="C18">
-        <v>171.3947112078576</v>
+        <v>169.8100616102042</v>
       </c>
       <c r="D18">
-        <v>157.3587112078576</v>
+        <v>157.6780616102042</v>
       </c>
       <c r="E18">
-        <v>-29.136</v>
+        <v>-27.232</v>
       </c>
       <c r="F18">
-        <v>30.464</v>
+        <v>32.368</v>
       </c>
       <c r="G18">
         <v>44.5</v>
@@ -2763,28 +2763,28 @@
         <v>36.438</v>
       </c>
       <c r="M18">
-        <v>1.5323392</v>
+        <v>1.6281104</v>
       </c>
       <c r="N18">
-        <v>34.9056608</v>
+        <v>34.80988960000001</v>
       </c>
       <c r="O18">
-        <v>5.23584912</v>
+        <v>5.221483440000001</v>
       </c>
       <c r="P18">
-        <v>29.66981168</v>
+        <v>29.58840616000001</v>
       </c>
       <c r="Q18">
-        <v>30.10681168</v>
+        <v>30.02540616000001</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1224198211555327</v>
+        <v>0.1232237769127691</v>
       </c>
       <c r="T18">
-        <v>0.9986131223950685</v>
+        <v>1.009091361013918</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>23.77933032059742</v>
+        <v>22.3805461840917</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1095440848375983</v>
+        <v>0.1094147199045492</v>
       </c>
       <c r="C19">
-        <v>169.8100616102042</v>
+        <v>168.2267108548151</v>
       </c>
       <c r="D19">
-        <v>157.6780616102042</v>
+        <v>157.998710854815</v>
       </c>
       <c r="E19">
-        <v>-27.232</v>
+        <v>-25.328</v>
       </c>
       <c r="F19">
-        <v>32.368</v>
+        <v>34.27200000000001</v>
       </c>
       <c r="G19">
         <v>44.5</v>
@@ -2845,28 +2845,28 @@
         <v>36.438</v>
       </c>
       <c r="M19">
-        <v>1.6281104</v>
+        <v>1.7238816</v>
       </c>
       <c r="N19">
-        <v>34.80988960000001</v>
+        <v>34.7141184</v>
       </c>
       <c r="O19">
-        <v>5.221483440000001</v>
+        <v>5.20711776</v>
       </c>
       <c r="P19">
-        <v>29.58840616000001</v>
+        <v>29.50700064</v>
       </c>
       <c r="Q19">
-        <v>30.02540616000001</v>
+        <v>29.94400064000001</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1232237769127691</v>
+        <v>0.1240473413470112</v>
       </c>
       <c r="T19">
-        <v>1.009091361013918</v>
+        <v>1.01982516642835</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>22.3805461840917</v>
+        <v>21.13718250719771</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1094147199045492</v>
+        <v>0.1092853549715</v>
       </c>
       <c r="C20">
-        <v>168.2267108548151</v>
+        <v>166.6446668816934</v>
       </c>
       <c r="D20">
-        <v>157.998710854815</v>
+        <v>158.3206668816934</v>
       </c>
       <c r="E20">
-        <v>-25.328</v>
+        <v>-23.424</v>
       </c>
       <c r="F20">
-        <v>34.272</v>
+        <v>36.176</v>
       </c>
       <c r="G20">
         <v>44.5</v>
@@ -2927,28 +2927,28 @@
         <v>36.438</v>
       </c>
       <c r="M20">
-        <v>1.7238816</v>
+        <v>1.8196528</v>
       </c>
       <c r="N20">
-        <v>34.7141184</v>
+        <v>34.6183472</v>
       </c>
       <c r="O20">
-        <v>5.20711776</v>
+        <v>5.19275208</v>
       </c>
       <c r="P20">
-        <v>29.50700064</v>
+        <v>29.42559512</v>
       </c>
       <c r="Q20">
-        <v>29.94400064000001</v>
+        <v>29.86259512000001</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1240473413470112</v>
+        <v>0.1248912407055556</v>
       </c>
       <c r="T20">
-        <v>1.01982516642835</v>
+        <v>1.030824004075237</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>21.13718250719771</v>
+        <v>20.0246992173452</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1092853549715</v>
+        <v>0.1091559900384509</v>
       </c>
       <c r="C21">
-        <v>166.6446668816934</v>
+        <v>165.0639376956924</v>
       </c>
       <c r="D21">
-        <v>158.3206668816934</v>
+        <v>158.6439376956924</v>
       </c>
       <c r="E21">
-        <v>-23.424</v>
+        <v>-21.52</v>
       </c>
       <c r="F21">
-        <v>36.176</v>
+        <v>38.08000000000001</v>
       </c>
       <c r="G21">
         <v>44.5</v>
@@ -3009,28 +3009,28 @@
         <v>36.438</v>
       </c>
       <c r="M21">
-        <v>1.8196528</v>
+        <v>1.915424</v>
       </c>
       <c r="N21">
-        <v>34.6183472</v>
+        <v>34.522576</v>
       </c>
       <c r="O21">
-        <v>5.19275208</v>
+        <v>5.1783864</v>
       </c>
       <c r="P21">
-        <v>29.42559512</v>
+        <v>29.3441896</v>
       </c>
       <c r="Q21">
-        <v>29.86259512000001</v>
+        <v>29.7811896</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1248912407055556</v>
+        <v>0.1257562375480636</v>
       </c>
       <c r="T21">
-        <v>1.030824004075237</v>
+        <v>1.042097812663296</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>20.0246992173452</v>
+        <v>19.02346425647794</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1091559900384509</v>
+        <v>0.1090266251054017</v>
       </c>
       <c r="C22">
-        <v>165.0639376956924</v>
+        <v>163.4845313671788</v>
       </c>
       <c r="D22">
-        <v>158.6439376956924</v>
+        <v>158.9685313671788</v>
       </c>
       <c r="E22">
-        <v>-21.52</v>
+        <v>-19.616</v>
       </c>
       <c r="F22">
-        <v>38.08000000000001</v>
+        <v>39.984</v>
       </c>
       <c r="G22">
         <v>44.5</v>
@@ -3091,28 +3091,28 @@
         <v>36.438</v>
       </c>
       <c r="M22">
-        <v>1.915424</v>
+        <v>2.0111952</v>
       </c>
       <c r="N22">
-        <v>34.522576</v>
+        <v>34.4268048</v>
       </c>
       <c r="O22">
-        <v>5.1783864</v>
+        <v>5.16402072</v>
       </c>
       <c r="P22">
-        <v>29.3441896</v>
+        <v>29.26278408</v>
       </c>
       <c r="Q22">
-        <v>29.7811896</v>
+        <v>29.69978408</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1257562375480636</v>
+        <v>0.1266431330448123</v>
       </c>
       <c r="T22">
-        <v>1.042097812663296</v>
+        <v>1.053657034127002</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>19.02346425647794</v>
+        <v>18.11758500616947</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1090266251054017</v>
+        <v>0.1088972601723526</v>
       </c>
       <c r="C23">
-        <v>163.4845313671788</v>
+        <v>161.9064560327041</v>
       </c>
       <c r="D23">
-        <v>158.9685313671788</v>
+        <v>159.2944560327041</v>
       </c>
       <c r="E23">
-        <v>-19.616</v>
+        <v>-17.712</v>
       </c>
       <c r="F23">
-        <v>39.984</v>
+        <v>41.888</v>
       </c>
       <c r="G23">
         <v>44.5</v>
@@ -3173,28 +3173,28 @@
         <v>36.438</v>
       </c>
       <c r="M23">
-        <v>2.0111952</v>
+        <v>2.1069664</v>
       </c>
       <c r="N23">
-        <v>34.4268048</v>
+        <v>34.3310336</v>
       </c>
       <c r="O23">
-        <v>5.16402072</v>
+        <v>5.149655040000001</v>
       </c>
       <c r="P23">
-        <v>29.26278408</v>
+        <v>29.18137856000001</v>
       </c>
       <c r="Q23">
-        <v>29.69978408</v>
+        <v>29.61837856000001</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1266431330448123</v>
+        <v>0.1275527694517341</v>
       </c>
       <c r="T23">
-        <v>1.053657034127002</v>
+        <v>1.06551264588465</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>18.11758500616947</v>
+        <v>17.29405841497995</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1088972601723526</v>
+        <v>0.1087678952393034</v>
       </c>
       <c r="C24">
-        <v>161.9064560327041</v>
+        <v>160.3297198956847</v>
       </c>
       <c r="D24">
-        <v>159.2944560327041</v>
+        <v>159.6217198956847</v>
       </c>
       <c r="E24">
-        <v>-17.712</v>
+        <v>-15.808</v>
       </c>
       <c r="F24">
-        <v>41.888</v>
+        <v>43.792</v>
       </c>
       <c r="G24">
         <v>44.5</v>
@@ -3255,28 +3255,28 @@
         <v>36.438</v>
       </c>
       <c r="M24">
-        <v>2.1069664</v>
+        <v>2.2027376</v>
       </c>
       <c r="N24">
-        <v>34.3310336</v>
+        <v>34.2352624</v>
       </c>
       <c r="O24">
-        <v>5.149655040000001</v>
+        <v>5.135289360000001</v>
       </c>
       <c r="P24">
-        <v>29.18137856000001</v>
+        <v>29.09997304</v>
       </c>
       <c r="Q24">
-        <v>29.61837856000001</v>
+        <v>29.53697304</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1275527694517341</v>
+        <v>0.1284860327783161</v>
       </c>
       <c r="T24">
-        <v>1.06551264588465</v>
+        <v>1.077676195610028</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>17.29405841497995</v>
+        <v>16.54214283171995</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1087678952393034</v>
+        <v>0.1086385303062543</v>
       </c>
       <c r="C25">
-        <v>160.3297198956847</v>
+        <v>158.7543312270901</v>
       </c>
       <c r="D25">
-        <v>159.6217198956847</v>
+        <v>159.9503312270901</v>
       </c>
       <c r="E25">
-        <v>-15.808</v>
+        <v>-13.904</v>
       </c>
       <c r="F25">
-        <v>43.792</v>
+        <v>45.69600000000001</v>
       </c>
       <c r="G25">
         <v>44.5</v>
@@ -3337,28 +3337,28 @@
         <v>36.438</v>
       </c>
       <c r="M25">
-        <v>2.2027376</v>
+        <v>2.2985088</v>
       </c>
       <c r="N25">
-        <v>34.2352624</v>
+        <v>34.1394912</v>
       </c>
       <c r="O25">
-        <v>5.135289360000001</v>
+        <v>5.12092368</v>
       </c>
       <c r="P25">
-        <v>29.09997304</v>
+        <v>29.01856752</v>
       </c>
       <c r="Q25">
-        <v>29.53697304</v>
+        <v>29.45556752</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1284860327783161</v>
+        <v>0.129443855666124</v>
       </c>
       <c r="T25">
-        <v>1.077676195610028</v>
+        <v>1.090159838749232</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>16.54214283171995</v>
+        <v>15.85288688039828</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1086385303062543</v>
+        <v>0.1085091653732051</v>
       </c>
       <c r="C26">
-        <v>158.7543312270901</v>
+        <v>157.1802983661397</v>
       </c>
       <c r="D26">
-        <v>159.9503312270901</v>
+        <v>160.2802983661397</v>
       </c>
       <c r="E26">
-        <v>-13.904</v>
+        <v>-12</v>
       </c>
       <c r="F26">
-        <v>45.696</v>
+        <v>47.6</v>
       </c>
       <c r="G26">
         <v>44.5</v>
@@ -3419,28 +3419,28 @@
         <v>36.438</v>
       </c>
       <c r="M26">
-        <v>2.2985088</v>
+        <v>2.39428</v>
       </c>
       <c r="N26">
-        <v>34.1394912</v>
+        <v>34.04372</v>
       </c>
       <c r="O26">
-        <v>5.12092368</v>
+        <v>5.106558</v>
       </c>
       <c r="P26">
-        <v>29.01856752</v>
+        <v>28.937162</v>
       </c>
       <c r="Q26">
-        <v>29.45556752</v>
+        <v>29.374162</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.129443855666124</v>
+        <v>0.1304272204976068</v>
       </c>
       <c r="T26">
-        <v>1.090159838749232</v>
+        <v>1.102976379038815</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>15.85288688039829</v>
+        <v>15.21877140518235</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1085091653732051</v>
+        <v>0.108379800440156</v>
       </c>
       <c r="C27">
-        <v>157.1802983661397</v>
+        <v>155.6076297210081</v>
       </c>
       <c r="D27">
-        <v>160.2802983661397</v>
+        <v>160.6116297210081</v>
       </c>
       <c r="E27">
-        <v>-12</v>
+        <v>-10.096</v>
       </c>
       <c r="F27">
-        <v>47.6</v>
+        <v>49.504</v>
       </c>
       <c r="G27">
         <v>44.5</v>
@@ -3501,28 +3501,28 @@
         <v>36.438</v>
       </c>
       <c r="M27">
-        <v>2.39428</v>
+        <v>2.4900512</v>
       </c>
       <c r="N27">
-        <v>34.04372</v>
+        <v>33.94794880000001</v>
       </c>
       <c r="O27">
-        <v>5.106558</v>
+        <v>5.092192320000001</v>
       </c>
       <c r="P27">
-        <v>28.937162</v>
+        <v>28.85575648</v>
       </c>
       <c r="Q27">
-        <v>29.374162</v>
+        <v>29.29275648</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1304272204976068</v>
+        <v>0.1314371627569675</v>
       </c>
       <c r="T27">
-        <v>1.102976379038815</v>
+        <v>1.116139312309198</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>15.21877140518235</v>
+        <v>14.63343404344457</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.108379800440156</v>
+        <v>0.1082504355071068</v>
       </c>
       <c r="C28">
-        <v>155.6076297210081</v>
+        <v>154.0363337695397</v>
       </c>
       <c r="D28">
-        <v>160.6116297210081</v>
+        <v>160.9443337695397</v>
       </c>
       <c r="E28">
-        <v>-10.096</v>
+        <v>-8.191999999999993</v>
       </c>
       <c r="F28">
-        <v>49.504</v>
+        <v>51.40800000000001</v>
       </c>
       <c r="G28">
         <v>44.5</v>
@@ -3583,28 +3583,28 @@
         <v>36.438</v>
       </c>
       <c r="M28">
-        <v>2.4900512</v>
+        <v>2.5858224</v>
       </c>
       <c r="N28">
-        <v>33.94794880000001</v>
+        <v>33.8521776</v>
       </c>
       <c r="O28">
-        <v>5.092192320000001</v>
+        <v>5.077826640000001</v>
       </c>
       <c r="P28">
-        <v>28.85575648</v>
+        <v>28.77435096</v>
       </c>
       <c r="Q28">
-        <v>29.29275648</v>
+        <v>29.21135096</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1314371627569675</v>
+        <v>0.1324747746672696</v>
       </c>
       <c r="T28">
-        <v>1.116139312309198</v>
+        <v>1.129662873888358</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>14.63343404344457</v>
+        <v>14.09145500479847</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1082504355071068</v>
+        <v>0.1081210705740577</v>
       </c>
       <c r="C29">
-        <v>154.0363337695397</v>
+        <v>152.4664190599711</v>
       </c>
       <c r="D29">
-        <v>160.9443337695397</v>
+        <v>161.2784190599712</v>
       </c>
       <c r="E29">
-        <v>-8.191999999999993</v>
+        <v>-6.287999999999997</v>
       </c>
       <c r="F29">
-        <v>51.40800000000001</v>
+        <v>53.312</v>
       </c>
       <c r="G29">
         <v>44.5</v>
@@ -3665,28 +3665,28 @@
         <v>36.438</v>
       </c>
       <c r="M29">
-        <v>2.5858224</v>
+        <v>2.6815936</v>
       </c>
       <c r="N29">
-        <v>33.8521776</v>
+        <v>33.7564064</v>
       </c>
       <c r="O29">
-        <v>5.077826640000001</v>
+        <v>5.06346096</v>
       </c>
       <c r="P29">
-        <v>28.77435096</v>
+        <v>28.69294544</v>
       </c>
       <c r="Q29">
-        <v>29.21135096</v>
+        <v>29.12994544</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1324747746672696</v>
+        <v>0.1335412091306357</v>
       </c>
       <c r="T29">
-        <v>1.129662873888358</v>
+        <v>1.143562089955828</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>14.09145500479847</v>
+        <v>13.5881887546271</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1081210705740577</v>
+        <v>0.1079917056410085</v>
       </c>
       <c r="C30">
-        <v>152.4664190599711</v>
+        <v>150.8978942116642</v>
       </c>
       <c r="D30">
-        <v>161.2784190599712</v>
+        <v>161.6138942116642</v>
       </c>
       <c r="E30">
-        <v>-6.287999999999997</v>
+        <v>-4.383999999999993</v>
       </c>
       <c r="F30">
-        <v>53.312</v>
+        <v>55.21600000000001</v>
       </c>
       <c r="G30">
         <v>44.5</v>
@@ -3747,28 +3747,28 @@
         <v>36.438</v>
       </c>
       <c r="M30">
-        <v>2.6815936</v>
+        <v>2.7773648</v>
       </c>
       <c r="N30">
-        <v>33.7564064</v>
+        <v>33.6606352</v>
       </c>
       <c r="O30">
-        <v>5.06346096</v>
+        <v>5.04909528</v>
       </c>
       <c r="P30">
-        <v>28.69294544</v>
+        <v>28.61153992</v>
       </c>
       <c r="Q30">
-        <v>29.12994544</v>
+        <v>29.04853992</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1335412091306357</v>
+        <v>0.1346376840014205</v>
       </c>
       <c r="T30">
-        <v>1.143562089955828</v>
+        <v>1.157852833236466</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>13.5881887546271</v>
+        <v>13.11963052170892</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1079917056410085</v>
+        <v>0.1082448407079594</v>
       </c>
       <c r="C31">
-        <v>150.8978942116643</v>
+        <v>148.3387537153855</v>
       </c>
       <c r="D31">
-        <v>161.6138942116643</v>
+        <v>160.9587537153855</v>
       </c>
       <c r="E31">
-        <v>-4.384</v>
+        <v>-2.480000000000004</v>
       </c>
       <c r="F31">
-        <v>55.216</v>
+        <v>57.12</v>
       </c>
       <c r="G31">
         <v>44.5</v>
@@ -3829,45 +3829,45 @@
         <v>36.438</v>
       </c>
       <c r="M31">
-        <v>2.7773648</v>
+        <v>2.958816</v>
       </c>
       <c r="N31">
-        <v>33.6606352</v>
+        <v>33.479184</v>
       </c>
       <c r="O31">
-        <v>5.04909528</v>
+        <v>5.021877600000001</v>
       </c>
       <c r="P31">
-        <v>28.61153992</v>
+        <v>28.4573064</v>
       </c>
       <c r="Q31">
-        <v>29.04853992</v>
+        <v>28.8943064</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1346376840014205</v>
+        <v>0.1357654867256562</v>
       </c>
       <c r="T31">
-        <v>1.157852833236466</v>
+        <v>1.17255188346798</v>
       </c>
       <c r="U31">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V31">
         <v>0.15</v>
       </c>
       <c r="W31">
-        <v>0.04275499999999999</v>
+        <v>0.04403</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y31">
-        <v>13.11963052170892</v>
+        <v>12.31506115959898</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1082448407079594</v>
+        <v>0.1081282257749102</v>
       </c>
       <c r="C32">
-        <v>148.3387537153855</v>
+        <v>146.7359045030878</v>
       </c>
       <c r="D32">
-        <v>160.9587537153855</v>
+        <v>161.2599045030878</v>
       </c>
       <c r="E32">
-        <v>-2.480000000000004</v>
+        <v>-0.5760000000000005</v>
       </c>
       <c r="F32">
-        <v>57.12</v>
+        <v>59.024</v>
       </c>
       <c r="G32">
         <v>44.5</v>
@@ -3911,28 +3911,28 @@
         <v>36.438</v>
       </c>
       <c r="M32">
-        <v>2.958816</v>
+        <v>3.0574432</v>
       </c>
       <c r="N32">
-        <v>33.479184</v>
+        <v>33.3805568</v>
       </c>
       <c r="O32">
-        <v>5.021877600000001</v>
+        <v>5.00708352</v>
       </c>
       <c r="P32">
-        <v>28.4573064</v>
+        <v>28.37347328</v>
       </c>
       <c r="Q32">
-        <v>28.8943064</v>
+        <v>28.81047328</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1357654867256562</v>
+        <v>0.1369259793839278</v>
       </c>
       <c r="T32">
-        <v>1.17255188346798</v>
+        <v>1.187676993126494</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>12.31506115959898</v>
+        <v>11.91780112219256</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1081282257749102</v>
+        <v>0.1080116108418611</v>
       </c>
       <c r="C33">
-        <v>146.7359045030878</v>
+        <v>145.1341842980113</v>
       </c>
       <c r="D33">
-        <v>161.2599045030878</v>
+        <v>161.5621842980113</v>
       </c>
       <c r="E33">
-        <v>-0.5760000000000005</v>
+        <v>1.328000000000003</v>
       </c>
       <c r="F33">
-        <v>59.024</v>
+        <v>60.928</v>
       </c>
       <c r="G33">
         <v>44.5</v>
@@ -3993,28 +3993,28 @@
         <v>36.438</v>
       </c>
       <c r="M33">
-        <v>3.0574432</v>
+        <v>3.1560704</v>
       </c>
       <c r="N33">
-        <v>33.3805568</v>
+        <v>33.28192960000001</v>
       </c>
       <c r="O33">
-        <v>5.00708352</v>
+        <v>4.99228944</v>
       </c>
       <c r="P33">
-        <v>28.37347328</v>
+        <v>28.28964016</v>
       </c>
       <c r="Q33">
-        <v>28.81047328</v>
+        <v>28.72664016000001</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1369259793839278</v>
+        <v>0.1381206041792074</v>
       </c>
       <c r="T33">
-        <v>1.187676993126494</v>
+        <v>1.203246958951435</v>
       </c>
       <c r="U33">
         <v>0.0518</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>11.91780112219256</v>
+        <v>11.54536983712404</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1080116108418611</v>
+        <v>0.1078949959088119</v>
       </c>
       <c r="C34">
-        <v>145.1341842980113</v>
+        <v>143.5335994610118</v>
       </c>
       <c r="D34">
-        <v>161.5621842980113</v>
+        <v>161.8655994610118</v>
       </c>
       <c r="E34">
-        <v>1.328000000000003</v>
+        <v>3.232000000000006</v>
       </c>
       <c r="F34">
-        <v>60.928</v>
+        <v>62.83200000000001</v>
       </c>
       <c r="G34">
         <v>44.5</v>
@@ -4075,28 +4075,28 @@
         <v>36.438</v>
       </c>
       <c r="M34">
-        <v>3.1560704</v>
+        <v>3.254697600000001</v>
       </c>
       <c r="N34">
-        <v>33.28192960000001</v>
+        <v>33.1833024</v>
       </c>
       <c r="O34">
-        <v>4.99228944</v>
+        <v>4.97749536</v>
       </c>
       <c r="P34">
-        <v>28.28964016</v>
+        <v>28.20580704</v>
       </c>
       <c r="Q34">
-        <v>28.72664016000001</v>
+        <v>28.64280704</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1381206041792074</v>
+        <v>0.1393508894161372</v>
       </c>
       <c r="T34">
-        <v>1.203246958951435</v>
+        <v>1.219281699875628</v>
       </c>
       <c r="U34">
         <v>0.0518</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>11.54536983712404</v>
+        <v>11.19551014508998</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1078949959088119</v>
+        <v>0.1077783809757628</v>
       </c>
       <c r="C35">
-        <v>143.5335994610118</v>
+        <v>141.9341564008178</v>
       </c>
       <c r="D35">
-        <v>161.8655994610118</v>
+        <v>162.1701564008177</v>
       </c>
       <c r="E35">
-        <v>3.232000000000006</v>
+        <v>5.136000000000003</v>
       </c>
       <c r="F35">
-        <v>62.83200000000001</v>
+        <v>64.736</v>
       </c>
       <c r="G35">
         <v>44.5</v>
@@ -4157,28 +4157,28 @@
         <v>36.438</v>
       </c>
       <c r="M35">
-        <v>3.254697600000001</v>
+        <v>3.3533248</v>
       </c>
       <c r="N35">
-        <v>33.1833024</v>
+        <v>33.0846752</v>
       </c>
       <c r="O35">
-        <v>4.97749536</v>
+        <v>4.96270128</v>
       </c>
       <c r="P35">
-        <v>28.20580704</v>
+        <v>28.12197392</v>
       </c>
       <c r="Q35">
-        <v>28.64280704</v>
+        <v>28.55897392</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1393508894161372</v>
+        <v>0.140618456023883</v>
       </c>
       <c r="T35">
-        <v>1.219281699875628</v>
+        <v>1.235802342039948</v>
       </c>
       <c r="U35">
         <v>0.0518</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>11.19551014508998</v>
+        <v>10.86623043494027</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1077783809757628</v>
+        <v>0.1076617660427136</v>
       </c>
       <c r="C36">
-        <v>141.9341564008178</v>
+        <v>140.3358615744818</v>
       </c>
       <c r="D36">
-        <v>162.1701564008177</v>
+        <v>162.4758615744818</v>
       </c>
       <c r="E36">
-        <v>5.136000000000003</v>
+        <v>7.040000000000013</v>
       </c>
       <c r="F36">
-        <v>64.736</v>
+        <v>66.64000000000001</v>
       </c>
       <c r="G36">
         <v>44.5</v>
@@ -4239,28 +4239,28 @@
         <v>36.438</v>
       </c>
       <c r="M36">
-        <v>3.3533248</v>
+        <v>3.451952000000001</v>
       </c>
       <c r="N36">
-        <v>33.0846752</v>
+        <v>32.986048</v>
       </c>
       <c r="O36">
-        <v>4.96270128</v>
+        <v>4.9479072</v>
       </c>
       <c r="P36">
-        <v>28.12197392</v>
+        <v>28.0381408</v>
       </c>
       <c r="Q36">
-        <v>28.55897392</v>
+        <v>28.47514080000001</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.140618456023883</v>
+        <v>0.1419250246810979</v>
       </c>
       <c r="T36">
-        <v>1.235802342039948</v>
+        <v>1.252831311655478</v>
       </c>
       <c r="U36">
         <v>0.0518</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>10.86623043494027</v>
+        <v>10.55576670822769</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1076617660427136</v>
+        <v>0.1075451511096644</v>
       </c>
       <c r="C37">
-        <v>140.3358615744818</v>
+        <v>138.7387214878369</v>
       </c>
       <c r="D37">
-        <v>162.4758615744818</v>
+        <v>162.7827214878369</v>
       </c>
       <c r="E37">
-        <v>7.040000000000013</v>
+        <v>8.94400000000001</v>
       </c>
       <c r="F37">
-        <v>66.64000000000001</v>
+        <v>68.54400000000001</v>
       </c>
       <c r="G37">
         <v>44.5</v>
@@ -4321,28 +4321,28 @@
         <v>36.438</v>
       </c>
       <c r="M37">
-        <v>3.451952000000001</v>
+        <v>3.5505792</v>
       </c>
       <c r="N37">
-        <v>32.986048</v>
+        <v>32.8874208</v>
       </c>
       <c r="O37">
-        <v>4.9479072</v>
+        <v>4.93311312</v>
       </c>
       <c r="P37">
-        <v>28.0381408</v>
+        <v>27.95430768</v>
       </c>
       <c r="Q37">
-        <v>28.47514080000001</v>
+        <v>28.39130768</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1419250246810979</v>
+        <v>0.1432724236088507</v>
       </c>
       <c r="T37">
-        <v>1.252831311655478</v>
+        <v>1.270392436571493</v>
       </c>
       <c r="U37">
         <v>0.0518</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>10.55576670822769</v>
+        <v>10.26255096633248</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1075451511096644</v>
+        <v>0.1074285361766153</v>
       </c>
       <c r="C38">
-        <v>138.7387214878369</v>
+        <v>137.1427426959581</v>
       </c>
       <c r="D38">
-        <v>162.7827214878369</v>
+        <v>163.0907426959581</v>
       </c>
       <c r="E38">
-        <v>8.943999999999996</v>
+        <v>10.84800000000001</v>
       </c>
       <c r="F38">
-        <v>68.544</v>
+        <v>70.44800000000001</v>
       </c>
       <c r="G38">
         <v>44.5</v>
@@ -4403,28 +4403,28 @@
         <v>36.438</v>
       </c>
       <c r="M38">
-        <v>3.5505792</v>
+        <v>3.6492064</v>
       </c>
       <c r="N38">
-        <v>32.8874208</v>
+        <v>32.78879360000001</v>
       </c>
       <c r="O38">
-        <v>4.93311312</v>
+        <v>4.918319040000001</v>
       </c>
       <c r="P38">
-        <v>27.95430768</v>
+        <v>27.87047456000001</v>
       </c>
       <c r="Q38">
-        <v>28.39130768</v>
+        <v>28.30747456000001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1432724236088507</v>
+        <v>0.1446625971057386</v>
       </c>
       <c r="T38">
-        <v>1.270392436571492</v>
+        <v>1.288511057516587</v>
       </c>
       <c r="U38">
         <v>0.0518</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>10.26255096633248</v>
+        <v>9.98518472399917</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1074285361766153</v>
+        <v>0.1078610212435662</v>
       </c>
       <c r="C39">
-        <v>137.1427426959581</v>
+        <v>134.1022111120335</v>
       </c>
       <c r="D39">
-        <v>163.0907426959581</v>
+        <v>161.9542111120335</v>
       </c>
       <c r="E39">
-        <v>10.84800000000001</v>
+        <v>12.752</v>
       </c>
       <c r="F39">
-        <v>70.44800000000001</v>
+        <v>72.352</v>
       </c>
       <c r="G39">
         <v>44.5</v>
@@ -4485,45 +4485,45 @@
         <v>36.438</v>
       </c>
       <c r="M39">
-        <v>3.6492064</v>
+        <v>3.870832</v>
       </c>
       <c r="N39">
-        <v>32.78879360000001</v>
+        <v>32.567168</v>
       </c>
       <c r="O39">
-        <v>4.918319040000001</v>
+        <v>4.8850752</v>
       </c>
       <c r="P39">
-        <v>27.87047456000001</v>
+        <v>27.6820928</v>
       </c>
       <c r="Q39">
-        <v>28.30747456000001</v>
+        <v>28.1190928</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1446625971057386</v>
+        <v>0.1460976149089777</v>
       </c>
       <c r="T39">
-        <v>1.288511057516587</v>
+        <v>1.307214150105073</v>
       </c>
       <c r="U39">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V39">
         <v>0.15</v>
       </c>
       <c r="W39">
-        <v>0.04403</v>
+        <v>0.04547499999999999</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y39">
-        <v>9.98518472399917</v>
+        <v>9.413480099368819</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1078610212435662</v>
+        <v>0.107758856310517</v>
       </c>
       <c r="C40">
-        <v>134.1022111120335</v>
+        <v>132.465259958971</v>
       </c>
       <c r="D40">
-        <v>161.9542111120335</v>
+        <v>162.221259958971</v>
       </c>
       <c r="E40">
-        <v>12.752</v>
+        <v>14.656</v>
       </c>
       <c r="F40">
-        <v>72.352</v>
+        <v>74.256</v>
       </c>
       <c r="G40">
         <v>44.5</v>
@@ -4567,28 +4567,28 @@
         <v>36.438</v>
       </c>
       <c r="M40">
-        <v>3.870832</v>
+        <v>3.972696</v>
       </c>
       <c r="N40">
-        <v>32.567168</v>
+        <v>32.465304</v>
       </c>
       <c r="O40">
-        <v>4.8850752</v>
+        <v>4.869795600000001</v>
       </c>
       <c r="P40">
-        <v>27.6820928</v>
+        <v>27.5955084</v>
       </c>
       <c r="Q40">
-        <v>28.1190928</v>
+        <v>28.0325084</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1460976149089777</v>
+        <v>0.1475796824762574</v>
       </c>
       <c r="T40">
-        <v>1.307214150105073</v>
+        <v>1.326530458844</v>
       </c>
       <c r="U40">
         <v>0.0535</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>9.413480099368819</v>
+        <v>9.172108814769619</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.107758856310517</v>
+        <v>0.1076566913774678</v>
       </c>
       <c r="C41">
-        <v>132.465259958971</v>
+        <v>130.8291909425686</v>
       </c>
       <c r="D41">
-        <v>162.221259958971</v>
+        <v>162.4891909425686</v>
       </c>
       <c r="E41">
-        <v>14.656</v>
+        <v>16.56000000000001</v>
       </c>
       <c r="F41">
-        <v>74.256</v>
+        <v>76.16000000000001</v>
       </c>
       <c r="G41">
         <v>44.5</v>
@@ -4649,28 +4649,28 @@
         <v>36.438</v>
       </c>
       <c r="M41">
-        <v>3.972696</v>
+        <v>4.074560000000001</v>
       </c>
       <c r="N41">
-        <v>32.465304</v>
+        <v>32.36344</v>
       </c>
       <c r="O41">
-        <v>4.869795600000001</v>
+        <v>4.854516</v>
       </c>
       <c r="P41">
-        <v>27.5955084</v>
+        <v>27.508924</v>
       </c>
       <c r="Q41">
-        <v>28.0325084</v>
+        <v>27.94592400000001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1475796824762574</v>
+        <v>0.1491111522957798</v>
       </c>
       <c r="T41">
-        <v>1.326530458844</v>
+        <v>1.346490644540892</v>
       </c>
       <c r="U41">
         <v>0.0535</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>9.172108814769619</v>
+        <v>8.942806094400376</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1076566913774678</v>
+        <v>0.1075545264444187</v>
       </c>
       <c r="C42">
-        <v>130.8291909425686</v>
+        <v>129.1940084409717</v>
       </c>
       <c r="D42">
-        <v>162.4891909425686</v>
+        <v>162.7580084409717</v>
       </c>
       <c r="E42">
-        <v>16.56000000000001</v>
+        <v>18.46400000000001</v>
       </c>
       <c r="F42">
-        <v>76.16000000000001</v>
+        <v>78.06400000000001</v>
       </c>
       <c r="G42">
         <v>44.5</v>
@@ -4731,28 +4731,28 @@
         <v>36.438</v>
       </c>
       <c r="M42">
-        <v>4.074560000000001</v>
+        <v>4.176424</v>
       </c>
       <c r="N42">
-        <v>32.36344</v>
+        <v>32.26157600000001</v>
       </c>
       <c r="O42">
-        <v>4.854516</v>
+        <v>4.839236400000001</v>
       </c>
       <c r="P42">
-        <v>27.508924</v>
+        <v>27.4223396</v>
       </c>
       <c r="Q42">
-        <v>27.94592400000001</v>
+        <v>27.85933960000001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1491111522957798</v>
+        <v>0.1506945363464724</v>
       </c>
       <c r="T42">
-        <v>1.346490644540892</v>
+        <v>1.367127446702084</v>
       </c>
       <c r="U42">
         <v>0.0535</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>8.942806094400376</v>
+        <v>8.724688872585734</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1075545264444187</v>
+        <v>0.1074523615113696</v>
       </c>
       <c r="C43">
-        <v>129.1940084409717</v>
+        <v>127.5597168613462</v>
       </c>
       <c r="D43">
-        <v>162.7580084409717</v>
+        <v>163.0277168613462</v>
       </c>
       <c r="E43">
-        <v>18.46400000000001</v>
+        <v>20.368</v>
       </c>
       <c r="F43">
-        <v>78.06400000000001</v>
+        <v>79.968</v>
       </c>
       <c r="G43">
         <v>44.5</v>
@@ -4813,28 +4813,28 @@
         <v>36.438</v>
       </c>
       <c r="M43">
-        <v>4.176424</v>
+        <v>4.278288</v>
       </c>
       <c r="N43">
-        <v>32.26157600000001</v>
+        <v>32.159712</v>
       </c>
       <c r="O43">
-        <v>4.839236400000001</v>
+        <v>4.823956799999999</v>
       </c>
       <c r="P43">
-        <v>27.4223396</v>
+        <v>27.3357552</v>
       </c>
       <c r="Q43">
-        <v>27.85933960000001</v>
+        <v>27.7727552</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1506945363464724</v>
+        <v>0.1523325198471889</v>
       </c>
       <c r="T43">
-        <v>1.367127446702084</v>
+        <v>1.388475862730905</v>
       </c>
       <c r="U43">
         <v>0.0535</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>8.724688872585734</v>
+        <v>8.516958185143217</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1074523615113696</v>
+        <v>0.1073501965783204</v>
       </c>
       <c r="C44">
-        <v>127.5597168613462</v>
+        <v>125.9263206401189</v>
       </c>
       <c r="D44">
-        <v>163.0277168613462</v>
+        <v>163.2983206401189</v>
       </c>
       <c r="E44">
-        <v>20.368</v>
+        <v>22.272</v>
       </c>
       <c r="F44">
-        <v>79.968</v>
+        <v>81.872</v>
       </c>
       <c r="G44">
         <v>44.5</v>
@@ -4895,28 +4895,28 @@
         <v>36.438</v>
       </c>
       <c r="M44">
-        <v>4.278288</v>
+        <v>4.380152</v>
       </c>
       <c r="N44">
-        <v>32.159712</v>
+        <v>32.057848</v>
       </c>
       <c r="O44">
-        <v>4.823956799999999</v>
+        <v>4.8086772</v>
       </c>
       <c r="P44">
-        <v>27.3357552</v>
+        <v>27.2491708</v>
       </c>
       <c r="Q44">
-        <v>27.7727552</v>
+        <v>27.6861708</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1523325198471889</v>
+        <v>0.1540279764531937</v>
       </c>
       <c r="T44">
-        <v>1.388475862730904</v>
+        <v>1.410573345988806</v>
       </c>
       <c r="U44">
         <v>0.0535</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>8.516958185143217</v>
+        <v>8.318889390139887</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1073501965783204</v>
+        <v>0.1072480316452713</v>
       </c>
       <c r="C45">
-        <v>125.9263206401189</v>
+        <v>124.2938242432212</v>
       </c>
       <c r="D45">
-        <v>163.2983206401189</v>
+        <v>163.5698242432211</v>
       </c>
       <c r="E45">
-        <v>22.272</v>
+        <v>24.17599999999999</v>
       </c>
       <c r="F45">
-        <v>81.872</v>
+        <v>83.776</v>
       </c>
       <c r="G45">
         <v>44.5</v>
@@ -4977,28 +4977,28 @@
         <v>36.438</v>
       </c>
       <c r="M45">
-        <v>4.380152</v>
+        <v>4.482016</v>
       </c>
       <c r="N45">
-        <v>32.057848</v>
+        <v>31.955984</v>
       </c>
       <c r="O45">
-        <v>4.8086772</v>
+        <v>4.7933976</v>
       </c>
       <c r="P45">
-        <v>27.2491708</v>
+        <v>27.1625864</v>
       </c>
       <c r="Q45">
-        <v>27.6861708</v>
+        <v>27.5995864</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1540279764531937</v>
+        <v>0.1557839850808415</v>
       </c>
       <c r="T45">
-        <v>1.410573345988806</v>
+        <v>1.433460025077347</v>
       </c>
       <c r="U45">
         <v>0.0535</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>8.318889390139887</v>
+        <v>8.129823722182161</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1072480316452713</v>
+        <v>0.1071458667122221</v>
       </c>
       <c r="C46">
-        <v>124.2938242432212</v>
+        <v>122.6622321663346</v>
       </c>
       <c r="D46">
-        <v>163.5698242432211</v>
+        <v>163.8422321663346</v>
       </c>
       <c r="E46">
-        <v>24.17599999999999</v>
+        <v>26.08000000000001</v>
       </c>
       <c r="F46">
-        <v>83.776</v>
+        <v>85.68000000000001</v>
       </c>
       <c r="G46">
         <v>44.5</v>
@@ -5059,28 +5059,28 @@
         <v>36.438</v>
       </c>
       <c r="M46">
-        <v>4.482016</v>
+        <v>4.583880000000001</v>
       </c>
       <c r="N46">
-        <v>31.955984</v>
+        <v>31.85412</v>
       </c>
       <c r="O46">
-        <v>4.7933976</v>
+        <v>4.778118</v>
       </c>
       <c r="P46">
-        <v>27.1625864</v>
+        <v>27.076002</v>
       </c>
       <c r="Q46">
-        <v>27.5995864</v>
+        <v>27.513002</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1557839850808415</v>
+        <v>0.1576038485676765</v>
       </c>
       <c r="T46">
-        <v>1.433460025077347</v>
+        <v>1.457178947041835</v>
       </c>
       <c r="U46">
         <v>0.0535</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>8.129823722182161</v>
+        <v>7.949160972800335</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1071458667122221</v>
+        <v>0.1070437017791729</v>
       </c>
       <c r="C47">
-        <v>122.6622321663346</v>
+        <v>121.0315489351389</v>
       </c>
       <c r="D47">
-        <v>163.8422321663346</v>
+        <v>164.1155489351389</v>
       </c>
       <c r="E47">
-        <v>26.08000000000001</v>
+        <v>27.984</v>
       </c>
       <c r="F47">
-        <v>85.68000000000001</v>
+        <v>87.584</v>
       </c>
       <c r="G47">
         <v>44.5</v>
@@ -5141,28 +5141,28 @@
         <v>36.438</v>
       </c>
       <c r="M47">
-        <v>4.583880000000001</v>
+        <v>4.685744</v>
       </c>
       <c r="N47">
-        <v>31.85412</v>
+        <v>31.752256</v>
       </c>
       <c r="O47">
-        <v>4.778118</v>
+        <v>4.762838400000001</v>
       </c>
       <c r="P47">
-        <v>27.076002</v>
+        <v>26.9894176</v>
       </c>
       <c r="Q47">
-        <v>27.513002</v>
+        <v>27.4264176</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1576038485676765</v>
+        <v>0.1594911144058758</v>
       </c>
       <c r="T47">
-        <v>1.457178947041835</v>
+        <v>1.4817763475976</v>
       </c>
       <c r="U47">
         <v>0.0535</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>7.949160972800335</v>
+        <v>7.776353125565546</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1070437017791729</v>
+        <v>0.1072611368461238</v>
       </c>
       <c r="C48">
-        <v>121.0315489351389</v>
+        <v>118.5469466683808</v>
       </c>
       <c r="D48">
-        <v>164.1155489351389</v>
+        <v>163.5349466683808</v>
       </c>
       <c r="E48">
-        <v>27.984</v>
+        <v>29.88800000000001</v>
       </c>
       <c r="F48">
-        <v>87.584</v>
+        <v>89.48800000000001</v>
       </c>
       <c r="G48">
         <v>44.5</v>
@@ -5223,45 +5223,45 @@
         <v>36.438</v>
       </c>
       <c r="M48">
-        <v>4.685744</v>
+        <v>4.859198400000001</v>
       </c>
       <c r="N48">
-        <v>31.752256</v>
+        <v>31.5788016</v>
       </c>
       <c r="O48">
-        <v>4.762838400000001</v>
+        <v>4.73682024</v>
       </c>
       <c r="P48">
-        <v>26.9894176</v>
+        <v>26.84198136</v>
       </c>
       <c r="Q48">
-        <v>27.4264176</v>
+        <v>27.27898136</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1594911144058758</v>
+        <v>0.1614495978228751</v>
       </c>
       <c r="T48">
-        <v>1.4817763475976</v>
+        <v>1.507301951947923</v>
       </c>
       <c r="U48">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V48">
         <v>0.15</v>
       </c>
       <c r="W48">
-        <v>0.04547499999999999</v>
+        <v>0.046155</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y48">
-        <v>7.776353125565546</v>
+        <v>7.498767697980801</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1072611368461238</v>
+        <v>0.1071657719130747</v>
       </c>
       <c r="C49">
-        <v>118.5469466683808</v>
+        <v>116.8970867004221</v>
       </c>
       <c r="D49">
-        <v>163.5349466683808</v>
+        <v>163.7890867004221</v>
       </c>
       <c r="E49">
-        <v>29.88800000000001</v>
+        <v>31.79200000000001</v>
       </c>
       <c r="F49">
-        <v>89.48800000000001</v>
+        <v>91.39200000000001</v>
       </c>
       <c r="G49">
         <v>44.5</v>
@@ -5305,28 +5305,28 @@
         <v>36.438</v>
       </c>
       <c r="M49">
-        <v>4.859198400000001</v>
+        <v>4.962585600000001</v>
       </c>
       <c r="N49">
-        <v>31.5788016</v>
+        <v>31.4754144</v>
       </c>
       <c r="O49">
-        <v>4.73682024</v>
+        <v>4.72131216</v>
       </c>
       <c r="P49">
-        <v>26.84198136</v>
+        <v>26.75410224</v>
       </c>
       <c r="Q49">
-        <v>27.27898136</v>
+        <v>27.19110224</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1614495978228751</v>
+        <v>0.1634834075251435</v>
       </c>
       <c r="T49">
-        <v>1.507301951947923</v>
+        <v>1.533809310311719</v>
       </c>
       <c r="U49">
         <v>0.0543</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>7.498767697980801</v>
+        <v>7.342543370939536</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1071657719130747</v>
+        <v>0.1070704069800255</v>
       </c>
       <c r="C50">
-        <v>116.8970867004221</v>
+        <v>115.2480178500138</v>
       </c>
       <c r="D50">
-        <v>163.7890867004221</v>
+        <v>164.0440178500138</v>
       </c>
       <c r="E50">
-        <v>31.79199999999999</v>
+        <v>33.69600000000001</v>
       </c>
       <c r="F50">
-        <v>91.392</v>
+        <v>93.29600000000001</v>
       </c>
       <c r="G50">
         <v>44.5</v>
@@ -5387,28 +5387,28 @@
         <v>36.438</v>
       </c>
       <c r="M50">
-        <v>4.9625856</v>
+        <v>5.065972800000001</v>
       </c>
       <c r="N50">
-        <v>31.4754144</v>
+        <v>31.3720272</v>
       </c>
       <c r="O50">
-        <v>4.72131216</v>
+        <v>4.70580408</v>
       </c>
       <c r="P50">
-        <v>26.75410224</v>
+        <v>26.66622312</v>
       </c>
       <c r="Q50">
-        <v>27.19110224</v>
+        <v>27.10322312</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1634834075251435</v>
+        <v>0.1655969744706382</v>
       </c>
       <c r="T50">
-        <v>1.533809310311719</v>
+        <v>1.561356172925076</v>
       </c>
       <c r="U50">
         <v>0.0543</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>7.342543370939537</v>
+        <v>7.19269554704281</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1070704069800255</v>
+        <v>0.1069750420469764</v>
       </c>
       <c r="C51">
-        <v>115.2480178500138</v>
+        <v>113.5997438169426</v>
       </c>
       <c r="D51">
-        <v>164.0440178500138</v>
+        <v>164.2997438169427</v>
       </c>
       <c r="E51">
-        <v>33.69600000000001</v>
+        <v>35.6</v>
       </c>
       <c r="F51">
-        <v>93.29600000000001</v>
+        <v>95.2</v>
       </c>
       <c r="G51">
         <v>44.5</v>
@@ -5469,28 +5469,28 @@
         <v>36.438</v>
       </c>
       <c r="M51">
-        <v>5.065972800000001</v>
+        <v>5.16936</v>
       </c>
       <c r="N51">
-        <v>31.3720272</v>
+        <v>31.26864</v>
       </c>
       <c r="O51">
-        <v>4.70580408</v>
+        <v>4.690296</v>
       </c>
       <c r="P51">
-        <v>26.66622312</v>
+        <v>26.578344</v>
       </c>
       <c r="Q51">
-        <v>27.10322312</v>
+        <v>27.015344</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1655969744706382</v>
+        <v>0.1677950840939527</v>
       </c>
       <c r="T51">
-        <v>1.561356172925076</v>
+        <v>1.590004910042968</v>
       </c>
       <c r="U51">
         <v>0.0543</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>7.19269554704281</v>
+        <v>7.048841636101955</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1069750420469764</v>
+        <v>0.1068796771139272</v>
       </c>
       <c r="C52">
-        <v>113.5997438169426</v>
+        <v>111.9522683241019</v>
       </c>
       <c r="D52">
-        <v>164.2997438169427</v>
+        <v>164.5562683241019</v>
       </c>
       <c r="E52">
-        <v>35.6</v>
+        <v>37.504</v>
       </c>
       <c r="F52">
-        <v>95.2</v>
+        <v>97.104</v>
       </c>
       <c r="G52">
         <v>44.5</v>
@@ -5551,28 +5551,28 @@
         <v>36.438</v>
       </c>
       <c r="M52">
-        <v>5.16936</v>
+        <v>5.2727472</v>
       </c>
       <c r="N52">
-        <v>31.26864</v>
+        <v>31.1652528</v>
       </c>
       <c r="O52">
-        <v>4.690296</v>
+        <v>4.67478792</v>
       </c>
       <c r="P52">
-        <v>26.578344</v>
+        <v>26.49046488</v>
       </c>
       <c r="Q52">
-        <v>27.015344</v>
+        <v>26.92746488</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1677950840939527</v>
+        <v>0.1700829124774025</v>
       </c>
       <c r="T52">
-        <v>1.590004910042968</v>
+        <v>1.619822983369752</v>
       </c>
       <c r="U52">
         <v>0.0543</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>7.048841636101955</v>
+        <v>6.910629055001916</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1068796771139272</v>
+        <v>0.106784312180878</v>
       </c>
       <c r="C53">
-        <v>111.9522683241019</v>
+        <v>110.3055951176714</v>
       </c>
       <c r="D53">
-        <v>164.5562683241019</v>
+        <v>164.8135951176714</v>
       </c>
       <c r="E53">
-        <v>37.504</v>
+        <v>39.40800000000001</v>
       </c>
       <c r="F53">
-        <v>97.104</v>
+        <v>99.00800000000001</v>
       </c>
       <c r="G53">
         <v>44.5</v>
@@ -5633,28 +5633,28 @@
         <v>36.438</v>
       </c>
       <c r="M53">
-        <v>5.2727472</v>
+        <v>5.376134400000001</v>
       </c>
       <c r="N53">
-        <v>31.1652528</v>
+        <v>31.0618656</v>
       </c>
       <c r="O53">
-        <v>4.67478792</v>
+        <v>4.65927984</v>
       </c>
       <c r="P53">
-        <v>26.49046488</v>
+        <v>26.40258576</v>
       </c>
       <c r="Q53">
-        <v>26.92746488</v>
+        <v>26.83958576</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1700829124774025</v>
+        <v>0.1724660670434959</v>
       </c>
       <c r="T53">
-        <v>1.619822983369752</v>
+        <v>1.650883476418487</v>
       </c>
       <c r="U53">
         <v>0.0543</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>6.910629055001916</v>
+        <v>6.777732342405725</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.106784312180878</v>
+        <v>0.1066889472478289</v>
       </c>
       <c r="C54">
-        <v>110.3055951176714</v>
+        <v>108.6597279673003</v>
       </c>
       <c r="D54">
-        <v>164.8135951176714</v>
+        <v>165.0717279673003</v>
       </c>
       <c r="E54">
-        <v>39.40800000000001</v>
+        <v>41.312</v>
       </c>
       <c r="F54">
-        <v>99.00800000000001</v>
+        <v>100.912</v>
       </c>
       <c r="G54">
         <v>44.5</v>
@@ -5715,28 +5715,28 @@
         <v>36.438</v>
       </c>
       <c r="M54">
-        <v>5.376134400000001</v>
+        <v>5.479521600000001</v>
       </c>
       <c r="N54">
-        <v>31.0618656</v>
+        <v>30.9584784</v>
       </c>
       <c r="O54">
-        <v>4.65927984</v>
+        <v>4.64377176</v>
       </c>
       <c r="P54">
-        <v>26.40258576</v>
+        <v>26.31470664</v>
       </c>
       <c r="Q54">
-        <v>26.83958576</v>
+        <v>26.75170664</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1724660670434959</v>
+        <v>0.1749506324421891</v>
       </c>
       <c r="T54">
-        <v>1.650883476418487</v>
+        <v>1.683265692575677</v>
       </c>
       <c r="U54">
         <v>0.0543</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>6.777732342405725</v>
+        <v>6.649850600096182</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1066889472478289</v>
+        <v>0.1065935823147798</v>
       </c>
       <c r="C55">
-        <v>108.6597279673003</v>
+        <v>107.0146706662911</v>
       </c>
       <c r="D55">
-        <v>165.0717279673003</v>
+        <v>165.3306706662912</v>
       </c>
       <c r="E55">
-        <v>41.312</v>
+        <v>43.21600000000002</v>
       </c>
       <c r="F55">
-        <v>100.912</v>
+        <v>102.816</v>
       </c>
       <c r="G55">
         <v>44.5</v>
@@ -5797,28 +5797,28 @@
         <v>36.438</v>
       </c>
       <c r="M55">
-        <v>5.479521600000001</v>
+        <v>5.582908800000001</v>
       </c>
       <c r="N55">
-        <v>30.9584784</v>
+        <v>30.8550912</v>
       </c>
       <c r="O55">
-        <v>4.64377176</v>
+        <v>4.62826368</v>
       </c>
       <c r="P55">
-        <v>26.31470664</v>
+        <v>26.22682752</v>
       </c>
       <c r="Q55">
-        <v>26.75170664</v>
+        <v>26.66382752</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1749506324421891</v>
+        <v>0.1775432224234342</v>
       </c>
       <c r="T55">
-        <v>1.683265692575677</v>
+        <v>1.717055831174485</v>
       </c>
       <c r="U55">
         <v>0.0543</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>6.649850600096182</v>
+        <v>6.52670521861292</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1065935823147798</v>
+        <v>0.1064982173817306</v>
       </c>
       <c r="C56">
-        <v>107.0146706662911</v>
+        <v>105.3704270317854</v>
       </c>
       <c r="D56">
-        <v>165.3306706662912</v>
+        <v>165.5904270317854</v>
       </c>
       <c r="E56">
-        <v>43.21600000000002</v>
+        <v>45.12000000000001</v>
       </c>
       <c r="F56">
-        <v>102.816</v>
+        <v>104.72</v>
       </c>
       <c r="G56">
         <v>44.5</v>
@@ -5879,28 +5879,28 @@
         <v>36.438</v>
       </c>
       <c r="M56">
-        <v>5.582908800000001</v>
+        <v>5.686296</v>
       </c>
       <c r="N56">
-        <v>30.8550912</v>
+        <v>30.751704</v>
       </c>
       <c r="O56">
-        <v>4.62826368</v>
+        <v>4.612755600000001</v>
       </c>
       <c r="P56">
-        <v>26.22682752</v>
+        <v>26.1389484</v>
       </c>
       <c r="Q56">
-        <v>26.66382752</v>
+        <v>26.57594840000001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1775432224234342</v>
+        <v>0.180251038626068</v>
       </c>
       <c r="T56">
-        <v>1.717055831174485</v>
+        <v>1.752347753711019</v>
       </c>
       <c r="U56">
         <v>0.0543</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>6.52670521861292</v>
+        <v>6.408037851001777</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1064982173817306</v>
+        <v>0.1064028524486814</v>
       </c>
       <c r="C57">
-        <v>105.3704270317854</v>
+        <v>103.7270009049516</v>
       </c>
       <c r="D57">
-        <v>165.5904270317854</v>
+        <v>165.8510009049516</v>
       </c>
       <c r="E57">
-        <v>45.12000000000001</v>
+        <v>47.02400000000001</v>
       </c>
       <c r="F57">
-        <v>104.72</v>
+        <v>106.624</v>
       </c>
       <c r="G57">
         <v>44.5</v>
@@ -5961,28 +5961,28 @@
         <v>36.438</v>
       </c>
       <c r="M57">
-        <v>5.686296</v>
+        <v>5.789683200000001</v>
       </c>
       <c r="N57">
-        <v>30.751704</v>
+        <v>30.6483168</v>
       </c>
       <c r="O57">
-        <v>4.612755600000001</v>
+        <v>4.597247520000001</v>
       </c>
       <c r="P57">
-        <v>26.1389484</v>
+        <v>26.05106928</v>
       </c>
       <c r="Q57">
-        <v>26.57594840000001</v>
+        <v>26.48806928</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.180251038626068</v>
+        <v>0.1830819373833669</v>
       </c>
       <c r="T57">
-        <v>1.752347753711019</v>
+        <v>1.789243854544666</v>
       </c>
       <c r="U57">
         <v>0.0543</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>6.408037851001777</v>
+        <v>6.293608603662459</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1064028524486814</v>
+        <v>0.1063074875156323</v>
       </c>
       <c r="C58">
-        <v>103.7270009049516</v>
+        <v>102.0843961511737</v>
       </c>
       <c r="D58">
-        <v>165.8510009049516</v>
+        <v>166.1123961511737</v>
       </c>
       <c r="E58">
-        <v>47.02400000000001</v>
+        <v>48.92800000000002</v>
       </c>
       <c r="F58">
-        <v>106.624</v>
+        <v>108.528</v>
       </c>
       <c r="G58">
         <v>44.5</v>
@@ -6043,28 +6043,28 @@
         <v>36.438</v>
       </c>
       <c r="M58">
-        <v>5.789683200000001</v>
+        <v>5.893070400000001</v>
       </c>
       <c r="N58">
-        <v>30.6483168</v>
+        <v>30.5449296</v>
       </c>
       <c r="O58">
-        <v>4.597247520000001</v>
+        <v>4.581739440000001</v>
       </c>
       <c r="P58">
-        <v>26.05106928</v>
+        <v>25.96319016</v>
       </c>
       <c r="Q58">
-        <v>26.48806928</v>
+        <v>26.40019016</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1830819373833669</v>
+        <v>0.1860445058503077</v>
       </c>
       <c r="T58">
-        <v>1.789243854544666</v>
+        <v>1.827856053091507</v>
       </c>
       <c r="U58">
         <v>0.0543</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>6.293608603662459</v>
+        <v>6.183194417633294</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1063074875156323</v>
+        <v>0.1067051225825831</v>
       </c>
       <c r="C59">
-        <v>102.0843961511737</v>
+        <v>99.09588780500999</v>
       </c>
       <c r="D59">
-        <v>166.1123961511737</v>
+        <v>165.02788780501</v>
       </c>
       <c r="E59">
-        <v>48.92800000000002</v>
+        <v>50.83200000000001</v>
       </c>
       <c r="F59">
-        <v>108.528</v>
+        <v>110.432</v>
       </c>
       <c r="G59">
         <v>44.5</v>
@@ -6125,45 +6125,45 @@
         <v>36.438</v>
       </c>
       <c r="M59">
-        <v>5.893070400000001</v>
+        <v>6.106889600000001</v>
       </c>
       <c r="N59">
-        <v>30.5449296</v>
+        <v>30.3311104</v>
       </c>
       <c r="O59">
-        <v>4.581739440000001</v>
+        <v>4.549666559999999</v>
       </c>
       <c r="P59">
-        <v>25.96319016</v>
+        <v>25.78144384</v>
       </c>
       <c r="Q59">
-        <v>26.40019016</v>
+        <v>26.21844384</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1860445058503077</v>
+        <v>0.1891481490061503</v>
       </c>
       <c r="T59">
-        <v>1.827856053091507</v>
+        <v>1.868306927759626</v>
       </c>
       <c r="U59">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V59">
         <v>0.15</v>
       </c>
       <c r="W59">
-        <v>0.046155</v>
+        <v>0.047005</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y59">
-        <v>6.183194417633294</v>
+        <v>5.966703573616264</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1067051225825831</v>
+        <v>0.106618257649534</v>
       </c>
       <c r="C60">
-        <v>99.09588780500998</v>
+        <v>97.42759229539568</v>
       </c>
       <c r="D60">
-        <v>165.02788780501</v>
+        <v>165.2635922953957</v>
       </c>
       <c r="E60">
-        <v>50.832</v>
+        <v>52.736</v>
       </c>
       <c r="F60">
-        <v>110.432</v>
+        <v>112.336</v>
       </c>
       <c r="G60">
         <v>44.5</v>
@@ -6207,28 +6207,28 @@
         <v>36.438</v>
       </c>
       <c r="M60">
-        <v>6.106889600000001</v>
+        <v>6.212180800000001</v>
       </c>
       <c r="N60">
-        <v>30.3311104</v>
+        <v>30.2258192</v>
       </c>
       <c r="O60">
-        <v>4.549666559999999</v>
+        <v>4.533872880000001</v>
       </c>
       <c r="P60">
-        <v>25.78144384</v>
+        <v>25.69194632</v>
       </c>
       <c r="Q60">
-        <v>26.21844384</v>
+        <v>26.12894632</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1891481490061503</v>
+        <v>0.1924031893891073</v>
       </c>
       <c r="T60">
-        <v>1.868306927759626</v>
+        <v>1.910731015826189</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>5.966703573616264</v>
+        <v>5.865573004571921</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.106618257649534</v>
+        <v>0.1065313927164848</v>
       </c>
       <c r="C61">
-        <v>97.42759229539568</v>
+        <v>95.75997104842735</v>
       </c>
       <c r="D61">
-        <v>165.2635922953957</v>
+        <v>165.4999710484273</v>
       </c>
       <c r="E61">
-        <v>52.736</v>
+        <v>54.63999999999999</v>
       </c>
       <c r="F61">
-        <v>112.336</v>
+        <v>114.24</v>
       </c>
       <c r="G61">
         <v>44.5</v>
@@ -6289,28 +6289,28 @@
         <v>36.438</v>
       </c>
       <c r="M61">
-        <v>6.212180800000001</v>
+        <v>6.317472</v>
       </c>
       <c r="N61">
-        <v>30.2258192</v>
+        <v>30.120528</v>
       </c>
       <c r="O61">
-        <v>4.533872880000001</v>
+        <v>4.518079200000001</v>
       </c>
       <c r="P61">
-        <v>25.69194632</v>
+        <v>25.6024488</v>
       </c>
       <c r="Q61">
-        <v>26.12894632</v>
+        <v>26.03944880000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1924031893891073</v>
+        <v>0.1958209817912121</v>
       </c>
       <c r="T61">
-        <v>1.910731015826189</v>
+        <v>1.955276308296081</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>5.865573004571921</v>
+        <v>5.767813454495723</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1065313927164848</v>
+        <v>0.1064445277834357</v>
       </c>
       <c r="C62">
-        <v>95.75997104842735</v>
+        <v>94.09302696147023</v>
       </c>
       <c r="D62">
-        <v>165.4999710484273</v>
+        <v>165.7370269614702</v>
       </c>
       <c r="E62">
-        <v>54.63999999999999</v>
+        <v>56.544</v>
       </c>
       <c r="F62">
-        <v>114.24</v>
+        <v>116.144</v>
       </c>
       <c r="G62">
         <v>44.5</v>
@@ -6371,28 +6371,28 @@
         <v>36.438</v>
       </c>
       <c r="M62">
-        <v>6.317472</v>
+        <v>6.4227632</v>
       </c>
       <c r="N62">
-        <v>30.120528</v>
+        <v>30.0152368</v>
       </c>
       <c r="O62">
-        <v>4.518079200000001</v>
+        <v>4.50228552</v>
       </c>
       <c r="P62">
-        <v>25.6024488</v>
+        <v>25.51295128</v>
       </c>
       <c r="Q62">
-        <v>26.03944880000001</v>
+        <v>25.94995128</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1958209817912121</v>
+        <v>0.199414045598553</v>
       </c>
       <c r="T62">
-        <v>1.955276308296081</v>
+        <v>2.002105974738788</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>5.767813454495723</v>
+        <v>5.673259135569563</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1064445277834357</v>
+        <v>0.1063576628503865</v>
       </c>
       <c r="C63">
-        <v>94.09302696147023</v>
+        <v>92.42676294851358</v>
       </c>
       <c r="D63">
-        <v>165.7370269614702</v>
+        <v>165.9747629485136</v>
       </c>
       <c r="E63">
-        <v>56.544</v>
+        <v>58.448</v>
       </c>
       <c r="F63">
-        <v>116.144</v>
+        <v>118.048</v>
       </c>
       <c r="G63">
         <v>44.5</v>
@@ -6453,28 +6453,28 @@
         <v>36.438</v>
       </c>
       <c r="M63">
-        <v>6.4227632</v>
+        <v>6.5280544</v>
       </c>
       <c r="N63">
-        <v>30.0152368</v>
+        <v>29.9099456</v>
       </c>
       <c r="O63">
-        <v>4.50228552</v>
+        <v>4.48649184</v>
       </c>
       <c r="P63">
-        <v>25.51295128</v>
+        <v>25.42345376</v>
       </c>
       <c r="Q63">
-        <v>25.94995128</v>
+        <v>25.86045376</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.199414045598553</v>
+        <v>0.203196218027333</v>
       </c>
       <c r="T63">
-        <v>2.002105974738788</v>
+        <v>2.051400360467954</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>5.673259135569563</v>
+        <v>5.581754955963602</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1063576628503865</v>
+        <v>0.1062707979173374</v>
       </c>
       <c r="C64">
-        <v>92.42676294851358</v>
+        <v>90.76118194029002</v>
       </c>
       <c r="D64">
-        <v>165.9747629485136</v>
+        <v>166.21318194029</v>
       </c>
       <c r="E64">
-        <v>58.448</v>
+        <v>60.352</v>
       </c>
       <c r="F64">
-        <v>118.048</v>
+        <v>119.952</v>
       </c>
       <c r="G64">
         <v>44.5</v>
@@ -6535,28 +6535,28 @@
         <v>36.438</v>
       </c>
       <c r="M64">
-        <v>6.5280544</v>
+        <v>6.6333456</v>
       </c>
       <c r="N64">
-        <v>29.9099456</v>
+        <v>29.8046544</v>
       </c>
       <c r="O64">
-        <v>4.48649184</v>
+        <v>4.47069816</v>
       </c>
       <c r="P64">
-        <v>25.42345376</v>
+        <v>25.33395624</v>
       </c>
       <c r="Q64">
-        <v>25.86045376</v>
+        <v>25.77095624</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.203196218027333</v>
+        <v>0.20718283220902</v>
       </c>
       <c r="T64">
-        <v>2.051400360467954</v>
+        <v>2.103359307587885</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>5.581754955963602</v>
+        <v>5.493155670948307</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1062707979173374</v>
+        <v>0.1061839329842882</v>
       </c>
       <c r="C65">
-        <v>90.76118194029002</v>
+        <v>89.09628688439638</v>
       </c>
       <c r="D65">
-        <v>166.21318194029</v>
+        <v>166.4522868843964</v>
       </c>
       <c r="E65">
-        <v>60.352</v>
+        <v>62.25600000000001</v>
       </c>
       <c r="F65">
-        <v>119.952</v>
+        <v>121.856</v>
       </c>
       <c r="G65">
         <v>44.5</v>
@@ -6617,28 +6617,28 @@
         <v>36.438</v>
       </c>
       <c r="M65">
-        <v>6.6333456</v>
+        <v>6.738636800000001</v>
       </c>
       <c r="N65">
-        <v>29.8046544</v>
+        <v>29.6993632</v>
       </c>
       <c r="O65">
-        <v>4.47069816</v>
+        <v>4.45490448</v>
       </c>
       <c r="P65">
-        <v>25.33395624</v>
+        <v>25.24445872</v>
       </c>
       <c r="Q65">
-        <v>25.77095624</v>
+        <v>25.68145872</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.20718283220902</v>
+        <v>0.2113909249563562</v>
       </c>
       <c r="T65">
-        <v>2.103359307587885</v>
+        <v>2.158204862881145</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>5.493155670948307</v>
+        <v>5.40732511358974</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1061839329842882</v>
+        <v>0.1060970680512391</v>
       </c>
       <c r="C66">
-        <v>89.09628688439638</v>
+        <v>87.43208074541472</v>
       </c>
       <c r="D66">
-        <v>166.4522868843964</v>
+        <v>166.6920807454147</v>
       </c>
       <c r="E66">
-        <v>62.25600000000001</v>
+        <v>64.16</v>
       </c>
       <c r="F66">
-        <v>121.856</v>
+        <v>123.76</v>
       </c>
       <c r="G66">
         <v>44.5</v>
@@ -6699,28 +6699,28 @@
         <v>36.438</v>
       </c>
       <c r="M66">
-        <v>6.738636800000001</v>
+        <v>6.843928000000001</v>
       </c>
       <c r="N66">
-        <v>29.6993632</v>
+        <v>29.594072</v>
       </c>
       <c r="O66">
-        <v>4.45490448</v>
+        <v>4.4391108</v>
       </c>
       <c r="P66">
-        <v>25.24445872</v>
+        <v>25.1549612</v>
       </c>
       <c r="Q66">
-        <v>25.68145872</v>
+        <v>25.5919612</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2113909249563562</v>
+        <v>0.2158394801463974</v>
       </c>
       <c r="T66">
-        <v>2.158204862881145</v>
+        <v>2.216184449905449</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>5.40732511358974</v>
+        <v>5.32413549645759</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1060970680512391</v>
+        <v>0.1060102031181899</v>
       </c>
       <c r="C67">
-        <v>87.43208074541472</v>
+        <v>85.76856650503504</v>
       </c>
       <c r="D67">
-        <v>166.6920807454147</v>
+        <v>166.9325665050351</v>
       </c>
       <c r="E67">
-        <v>64.16</v>
+        <v>66.06400000000002</v>
       </c>
       <c r="F67">
-        <v>123.76</v>
+        <v>125.664</v>
       </c>
       <c r="G67">
         <v>44.5</v>
@@ -6781,28 +6781,28 @@
         <v>36.438</v>
       </c>
       <c r="M67">
-        <v>6.843928000000001</v>
+        <v>6.949219200000001</v>
       </c>
       <c r="N67">
-        <v>29.594072</v>
+        <v>29.4887808</v>
       </c>
       <c r="O67">
-        <v>4.4391108</v>
+        <v>4.42331712</v>
       </c>
       <c r="P67">
-        <v>25.1549612</v>
+        <v>25.06546368</v>
       </c>
       <c r="Q67">
-        <v>25.5919612</v>
+        <v>25.50246368</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2158394801463974</v>
+        <v>0.2205497150534998</v>
       </c>
       <c r="T67">
-        <v>2.216184449905449</v>
+        <v>2.277574600872359</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>5.32413549645759</v>
+        <v>5.243466776814293</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1060102031181899</v>
+        <v>0.1059233381851408</v>
       </c>
       <c r="C68">
-        <v>85.76856650503504</v>
+        <v>84.10574716217906</v>
       </c>
       <c r="D68">
-        <v>166.9325665050351</v>
+        <v>167.1737471621791</v>
       </c>
       <c r="E68">
-        <v>66.06400000000002</v>
+        <v>67.96800000000002</v>
       </c>
       <c r="F68">
-        <v>125.664</v>
+        <v>127.568</v>
       </c>
       <c r="G68">
         <v>44.5</v>
@@ -6863,28 +6863,28 @@
         <v>36.438</v>
       </c>
       <c r="M68">
-        <v>6.949219200000001</v>
+        <v>7.054510400000001</v>
       </c>
       <c r="N68">
-        <v>29.4887808</v>
+        <v>29.3834896</v>
       </c>
       <c r="O68">
-        <v>4.42331712</v>
+        <v>4.40752344</v>
       </c>
       <c r="P68">
-        <v>25.06546368</v>
+        <v>24.97596616</v>
       </c>
       <c r="Q68">
-        <v>25.50246368</v>
+        <v>25.41296616</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2205497150534998</v>
+        <v>0.2255454187428509</v>
       </c>
       <c r="T68">
-        <v>2.277574600872359</v>
+        <v>2.342685367049385</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>5.243466776814293</v>
+        <v>5.165206078652886</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1059233381851408</v>
+        <v>0.1058364732520916</v>
       </c>
       <c r="C69">
-        <v>84.10574716217906</v>
+        <v>82.44362573312449</v>
       </c>
       <c r="D69">
-        <v>167.1737471621791</v>
+        <v>167.4156257331245</v>
       </c>
       <c r="E69">
-        <v>67.96800000000002</v>
+        <v>69.87200000000001</v>
       </c>
       <c r="F69">
-        <v>127.568</v>
+        <v>129.472</v>
       </c>
       <c r="G69">
         <v>44.5</v>
@@ -6945,28 +6945,28 @@
         <v>36.438</v>
       </c>
       <c r="M69">
-        <v>7.054510400000001</v>
+        <v>7.159801600000001</v>
       </c>
       <c r="N69">
-        <v>29.3834896</v>
+        <v>29.2781984</v>
       </c>
       <c r="O69">
-        <v>4.40752344</v>
+        <v>4.39172976</v>
       </c>
       <c r="P69">
-        <v>24.97596616</v>
+        <v>24.88646864</v>
       </c>
       <c r="Q69">
-        <v>25.41296616</v>
+        <v>25.32346864</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2255454187428509</v>
+        <v>0.2308533539127864</v>
       </c>
       <c r="T69">
-        <v>2.342685367049385</v>
+        <v>2.411865556112474</v>
       </c>
       <c r="U69">
         <v>0.0553</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>5.165206078652886</v>
+        <v>5.089247165731519</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1058364732520916</v>
+        <v>0.1057496083190425</v>
       </c>
       <c r="C70">
-        <v>82.44362573312449</v>
+        <v>80.78220525163101</v>
       </c>
       <c r="D70">
-        <v>167.4156257331245</v>
+        <v>167.658205251631</v>
       </c>
       <c r="E70">
-        <v>69.87200000000001</v>
+        <v>71.77600000000001</v>
       </c>
       <c r="F70">
-        <v>129.472</v>
+        <v>131.376</v>
       </c>
       <c r="G70">
         <v>44.5</v>
@@ -7027,28 +7027,28 @@
         <v>36.438</v>
       </c>
       <c r="M70">
-        <v>7.159801600000001</v>
+        <v>7.265092800000001</v>
       </c>
       <c r="N70">
-        <v>29.2781984</v>
+        <v>29.1729072</v>
       </c>
       <c r="O70">
-        <v>4.39172976</v>
+        <v>4.37593608</v>
       </c>
       <c r="P70">
-        <v>24.88646864</v>
+        <v>24.79697112</v>
       </c>
       <c r="Q70">
-        <v>25.32346864</v>
+        <v>25.23397112</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2308533539127864</v>
+        <v>0.2365037365130403</v>
       </c>
       <c r="T70">
-        <v>2.411865556112474</v>
+        <v>2.485508983179635</v>
       </c>
       <c r="U70">
         <v>0.0553</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>5.089247165731519</v>
+        <v>5.015489960431062</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1057496083190425</v>
+        <v>0.1056627433859933</v>
       </c>
       <c r="C71">
-        <v>80.78220525163101</v>
+        <v>79.12148876906718</v>
       </c>
       <c r="D71">
-        <v>167.658205251631</v>
+        <v>167.9014887690672</v>
       </c>
       <c r="E71">
-        <v>71.77600000000001</v>
+        <v>73.68000000000004</v>
       </c>
       <c r="F71">
-        <v>131.376</v>
+        <v>133.28</v>
       </c>
       <c r="G71">
         <v>44.5</v>
@@ -7109,28 +7109,28 @@
         <v>36.438</v>
       </c>
       <c r="M71">
-        <v>7.265092800000001</v>
+        <v>7.370384000000002</v>
       </c>
       <c r="N71">
-        <v>29.1729072</v>
+        <v>29.067616</v>
       </c>
       <c r="O71">
-        <v>4.37593608</v>
+        <v>4.3601424</v>
       </c>
       <c r="P71">
-        <v>24.79697112</v>
+        <v>24.7074736</v>
       </c>
       <c r="Q71">
-        <v>25.23397112</v>
+        <v>25.1444736</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2365037365130403</v>
+        <v>0.2425308112866445</v>
       </c>
       <c r="T71">
-        <v>2.485508983179635</v>
+        <v>2.564061972051273</v>
       </c>
       <c r="U71">
         <v>0.0553</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>5.015489960431062</v>
+        <v>4.943840103853475</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1056627433859933</v>
+        <v>0.1055758784529442</v>
       </c>
       <c r="C72">
-        <v>79.12148876906718</v>
+        <v>77.46147935453814</v>
       </c>
       <c r="D72">
-        <v>167.9014887690672</v>
+        <v>168.1454793545382</v>
       </c>
       <c r="E72">
-        <v>73.68000000000004</v>
+        <v>75.58400000000003</v>
       </c>
       <c r="F72">
-        <v>133.28</v>
+        <v>135.184</v>
       </c>
       <c r="G72">
         <v>44.5</v>
@@ -7191,28 +7191,28 @@
         <v>36.438</v>
       </c>
       <c r="M72">
-        <v>7.370384000000002</v>
+        <v>7.475675200000001</v>
       </c>
       <c r="N72">
-        <v>29.067616</v>
+        <v>28.9623248</v>
       </c>
       <c r="O72">
-        <v>4.3601424</v>
+        <v>4.34434872</v>
       </c>
       <c r="P72">
-        <v>24.7074736</v>
+        <v>24.61797608</v>
       </c>
       <c r="Q72">
-        <v>25.1444736</v>
+        <v>25.05497608</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2425308112866445</v>
+        <v>0.2489735463894628</v>
       </c>
       <c r="T72">
-        <v>2.564061972051273</v>
+        <v>2.648032408431299</v>
       </c>
       <c r="U72">
         <v>0.0553</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>4.943840103853475</v>
+        <v>4.874208553094975</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1055758784529442</v>
+        <v>0.105489013519895</v>
       </c>
       <c r="C73">
-        <v>77.46147935453828</v>
+        <v>75.80218009501505</v>
       </c>
       <c r="D73">
-        <v>168.1454793545383</v>
+        <v>168.390180095015</v>
       </c>
       <c r="E73">
-        <v>75.584</v>
+        <v>77.488</v>
       </c>
       <c r="F73">
-        <v>135.184</v>
+        <v>137.088</v>
       </c>
       <c r="G73">
         <v>44.5</v>
@@ -7273,28 +7273,28 @@
         <v>36.438</v>
       </c>
       <c r="M73">
-        <v>7.4756752</v>
+        <v>7.5809664</v>
       </c>
       <c r="N73">
-        <v>28.9623248</v>
+        <v>28.8570336</v>
       </c>
       <c r="O73">
-        <v>4.34434872</v>
+        <v>4.32855504</v>
       </c>
       <c r="P73">
-        <v>24.61797608</v>
+        <v>24.52847856</v>
       </c>
       <c r="Q73">
-        <v>25.05497608</v>
+        <v>24.96547856</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2489735463894627</v>
+        <v>0.255876476856768</v>
       </c>
       <c r="T73">
-        <v>2.648032408431298</v>
+        <v>2.738000733124183</v>
       </c>
       <c r="U73">
         <v>0.0553</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>4.874208553094976</v>
+        <v>4.806511212079768</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.105489013519895</v>
+        <v>0.1054021485868459</v>
       </c>
       <c r="C74">
-        <v>75.80218009501505</v>
+        <v>74.14359409546464</v>
       </c>
       <c r="D74">
-        <v>168.390180095015</v>
+        <v>168.6355940954646</v>
       </c>
       <c r="E74">
-        <v>77.488</v>
+        <v>79.392</v>
       </c>
       <c r="F74">
-        <v>137.088</v>
+        <v>138.992</v>
       </c>
       <c r="G74">
         <v>44.5</v>
@@ -7355,28 +7355,28 @@
         <v>36.438</v>
       </c>
       <c r="M74">
-        <v>7.5809664</v>
+        <v>7.686257599999999</v>
       </c>
       <c r="N74">
-        <v>28.8570336</v>
+        <v>28.7517424</v>
       </c>
       <c r="O74">
-        <v>4.32855504</v>
+        <v>4.312761360000001</v>
       </c>
       <c r="P74">
-        <v>24.52847856</v>
+        <v>24.43898104000001</v>
       </c>
       <c r="Q74">
-        <v>24.96547856</v>
+        <v>24.87598104000001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.255876476856768</v>
+        <v>0.2632907355068366</v>
       </c>
       <c r="T74">
-        <v>2.738000733124183</v>
+        <v>2.83463337816469</v>
       </c>
       <c r="U74">
         <v>0.0553</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>4.806511212079768</v>
+        <v>4.740668592736212</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1054021485868459</v>
+        <v>0.1053152836537967</v>
       </c>
       <c r="C75">
-        <v>74.14359409546464</v>
+        <v>72.48572447898121</v>
       </c>
       <c r="D75">
-        <v>168.6355940954646</v>
+        <v>168.8817244789812</v>
       </c>
       <c r="E75">
-        <v>79.392</v>
+        <v>81.29600000000002</v>
       </c>
       <c r="F75">
-        <v>138.992</v>
+        <v>140.896</v>
       </c>
       <c r="G75">
         <v>44.5</v>
@@ -7437,28 +7437,28 @@
         <v>36.438</v>
       </c>
       <c r="M75">
-        <v>7.686257599999999</v>
+        <v>7.791548800000001</v>
       </c>
       <c r="N75">
-        <v>28.7517424</v>
+        <v>28.6464512</v>
       </c>
       <c r="O75">
-        <v>4.312761360000001</v>
+        <v>4.29696768</v>
       </c>
       <c r="P75">
-        <v>24.43898104000001</v>
+        <v>24.34948352</v>
       </c>
       <c r="Q75">
-        <v>24.87598104000001</v>
+        <v>24.78648352</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2632907355068366</v>
+        <v>0.271275321745372</v>
       </c>
       <c r="T75">
-        <v>2.83463337816469</v>
+        <v>2.938699303592927</v>
       </c>
       <c r="U75">
         <v>0.0553</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>4.740668592736212</v>
+        <v>4.67660550364518</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1053152836537967</v>
+        <v>0.1052284187207476</v>
       </c>
       <c r="C76">
-        <v>72.48572447898121</v>
+        <v>70.82857438691875</v>
       </c>
       <c r="D76">
-        <v>168.8817244789812</v>
+        <v>169.1285743869188</v>
       </c>
       <c r="E76">
-        <v>81.29600000000002</v>
+        <v>83.20000000000002</v>
       </c>
       <c r="F76">
-        <v>140.896</v>
+        <v>142.8</v>
       </c>
       <c r="G76">
         <v>44.5</v>
@@ -7519,28 +7519,28 @@
         <v>36.438</v>
       </c>
       <c r="M76">
-        <v>7.791548800000001</v>
+        <v>7.896840000000001</v>
       </c>
       <c r="N76">
-        <v>28.6464512</v>
+        <v>28.54116</v>
       </c>
       <c r="O76">
-        <v>4.29696768</v>
+        <v>4.281174</v>
       </c>
       <c r="P76">
-        <v>24.34948352</v>
+        <v>24.259986</v>
       </c>
       <c r="Q76">
-        <v>24.78648352</v>
+        <v>24.696986</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.271275321745372</v>
+        <v>0.2798986748829903</v>
       </c>
       <c r="T76">
-        <v>2.938699303592927</v>
+        <v>3.051090503055424</v>
       </c>
       <c r="U76">
         <v>0.0553</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>4.67660550364518</v>
+        <v>4.614250763596578</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1052284187207476</v>
+        <v>0.1051415537876984</v>
       </c>
       <c r="C77">
-        <v>70.82857438691875</v>
+        <v>69.17214697902477</v>
       </c>
       <c r="D77">
-        <v>169.1285743869188</v>
+        <v>169.3761469790248</v>
       </c>
       <c r="E77">
-        <v>83.20000000000002</v>
+        <v>85.10400000000001</v>
       </c>
       <c r="F77">
-        <v>142.8</v>
+        <v>144.704</v>
       </c>
       <c r="G77">
         <v>44.5</v>
@@ -7601,28 +7601,28 @@
         <v>36.438</v>
       </c>
       <c r="M77">
-        <v>7.896840000000001</v>
+        <v>8.002131200000001</v>
       </c>
       <c r="N77">
-        <v>28.54116</v>
+        <v>28.4358688</v>
       </c>
       <c r="O77">
-        <v>4.281174</v>
+        <v>4.26538032</v>
       </c>
       <c r="P77">
-        <v>24.259986</v>
+        <v>24.17048848</v>
       </c>
       <c r="Q77">
-        <v>24.696986</v>
+        <v>24.60748848</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2798986748829903</v>
+        <v>0.2892406407820768</v>
       </c>
       <c r="T77">
-        <v>3.051090503055424</v>
+        <v>3.172847635806462</v>
       </c>
       <c r="U77">
         <v>0.0553</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>4.614250763596578</v>
+        <v>4.55353693775978</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1051415537876984</v>
+        <v>0.1066909388546493</v>
       </c>
       <c r="C78">
-        <v>69.17214697902477</v>
+        <v>62.95832883919596</v>
       </c>
       <c r="D78">
-        <v>169.3761469790248</v>
+        <v>165.066328839196</v>
       </c>
       <c r="E78">
-        <v>85.10400000000001</v>
+        <v>87.00800000000001</v>
       </c>
       <c r="F78">
-        <v>144.704</v>
+        <v>146.608</v>
       </c>
       <c r="G78">
         <v>44.5</v>
@@ -7683,45 +7683,45 @@
         <v>36.438</v>
       </c>
       <c r="M78">
-        <v>8.002131200000001</v>
+        <v>8.4739424</v>
       </c>
       <c r="N78">
-        <v>28.4358688</v>
+        <v>27.9640576</v>
       </c>
       <c r="O78">
-        <v>4.26538032</v>
+        <v>4.19460864</v>
       </c>
       <c r="P78">
-        <v>24.17048848</v>
+        <v>23.76944896000001</v>
       </c>
       <c r="Q78">
-        <v>24.60748848</v>
+        <v>24.20644896000001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2892406407820768</v>
+        <v>0.2993949515419534</v>
       </c>
       <c r="T78">
-        <v>3.172847635806462</v>
+        <v>3.30519234531846</v>
       </c>
       <c r="U78">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V78">
         <v>0.15</v>
       </c>
       <c r="W78">
-        <v>0.047005</v>
+        <v>0.04913</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y78">
-        <v>4.55353693775978</v>
+        <v>4.300005626660857</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1066909388546493</v>
+        <v>0.1066253239216001</v>
       </c>
       <c r="C79">
-        <v>62.95832883919596</v>
+        <v>61.2323930962711</v>
       </c>
       <c r="D79">
-        <v>165.066328839196</v>
+        <v>165.2443930962711</v>
       </c>
       <c r="E79">
-        <v>87.00800000000001</v>
+        <v>88.91200000000001</v>
       </c>
       <c r="F79">
-        <v>146.608</v>
+        <v>148.512</v>
       </c>
       <c r="G79">
         <v>44.5</v>
@@ -7765,28 +7765,28 @@
         <v>36.438</v>
       </c>
       <c r="M79">
-        <v>8.4739424</v>
+        <v>8.583993600000001</v>
       </c>
       <c r="N79">
-        <v>27.9640576</v>
+        <v>27.8540064</v>
       </c>
       <c r="O79">
-        <v>4.19460864</v>
+        <v>4.17810096</v>
       </c>
       <c r="P79">
-        <v>23.76944896000001</v>
+        <v>23.67590544</v>
       </c>
       <c r="Q79">
-        <v>24.20644896000001</v>
+        <v>24.11290544</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2993949515419534</v>
+        <v>0.3104723814618188</v>
       </c>
       <c r="T79">
-        <v>3.30519234531846</v>
+        <v>3.449568392058822</v>
       </c>
       <c r="U79">
         <v>0.0578</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>4.300005626660857</v>
+        <v>4.244877349395973</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1066253239216001</v>
+        <v>0.106559708988551</v>
       </c>
       <c r="C80">
-        <v>61.2323930962711</v>
+        <v>59.50684193959592</v>
       </c>
       <c r="D80">
-        <v>165.2443930962711</v>
+        <v>165.4228419395959</v>
       </c>
       <c r="E80">
-        <v>88.91200000000001</v>
+        <v>90.81600000000003</v>
       </c>
       <c r="F80">
-        <v>148.512</v>
+        <v>150.416</v>
       </c>
       <c r="G80">
         <v>44.5</v>
@@ -7847,28 +7847,28 @@
         <v>36.438</v>
       </c>
       <c r="M80">
-        <v>8.583993600000001</v>
+        <v>8.694044800000002</v>
       </c>
       <c r="N80">
-        <v>27.8540064</v>
+        <v>27.7439552</v>
       </c>
       <c r="O80">
-        <v>4.17810096</v>
+        <v>4.16159328</v>
       </c>
       <c r="P80">
-        <v>23.67590544</v>
+        <v>23.58236192</v>
       </c>
       <c r="Q80">
-        <v>24.11290544</v>
+        <v>24.01936192000001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3104723814618188</v>
+        <v>0.3226048047073856</v>
       </c>
       <c r="T80">
-        <v>3.449568392058822</v>
+        <v>3.607694538488741</v>
       </c>
       <c r="U80">
         <v>0.0578</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>4.244877349395973</v>
+        <v>4.191144724720075</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.106559708988551</v>
+        <v>0.1064940940555018</v>
       </c>
       <c r="C81">
-        <v>59.50684193959592</v>
+        <v>57.78167661647137</v>
       </c>
       <c r="D81">
-        <v>165.4228419395959</v>
+        <v>165.6016766164714</v>
       </c>
       <c r="E81">
-        <v>90.81600000000003</v>
+        <v>92.72000000000003</v>
       </c>
       <c r="F81">
-        <v>150.416</v>
+        <v>152.32</v>
       </c>
       <c r="G81">
         <v>44.5</v>
@@ -7929,28 +7929,28 @@
         <v>36.438</v>
       </c>
       <c r="M81">
-        <v>8.694044800000002</v>
+        <v>8.804096000000001</v>
       </c>
       <c r="N81">
-        <v>27.7439552</v>
+        <v>27.633904</v>
       </c>
       <c r="O81">
-        <v>4.16159328</v>
+        <v>4.1450856</v>
       </c>
       <c r="P81">
-        <v>23.58236192</v>
+        <v>23.4888184</v>
       </c>
       <c r="Q81">
-        <v>24.01936192000001</v>
+        <v>23.9258184</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3226048047073856</v>
+        <v>0.3359504702775091</v>
       </c>
       <c r="T81">
-        <v>3.607694538488741</v>
+        <v>3.781633299561653</v>
       </c>
       <c r="U81">
         <v>0.0578</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>4.191144724720075</v>
+        <v>4.138755415661073</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1064940940555018</v>
+        <v>0.1064284791224527</v>
       </c>
       <c r="C82">
-        <v>57.78167661647137</v>
+        <v>56.0568983795981</v>
       </c>
       <c r="D82">
-        <v>165.6016766164714</v>
+        <v>165.7808983795981</v>
       </c>
       <c r="E82">
-        <v>92.72000000000003</v>
+        <v>94.62400000000002</v>
       </c>
       <c r="F82">
-        <v>152.32</v>
+        <v>154.224</v>
       </c>
       <c r="G82">
         <v>44.5</v>
@@ -8011,28 +8011,28 @@
         <v>36.438</v>
       </c>
       <c r="M82">
-        <v>8.804096000000001</v>
+        <v>8.914147200000002</v>
       </c>
       <c r="N82">
-        <v>27.633904</v>
+        <v>27.5238528</v>
       </c>
       <c r="O82">
-        <v>4.1450856</v>
+        <v>4.12857792</v>
       </c>
       <c r="P82">
-        <v>23.4888184</v>
+        <v>23.39527488</v>
       </c>
       <c r="Q82">
-        <v>23.9258184</v>
+        <v>23.83227488</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3359504702775091</v>
+        <v>0.350700942749751</v>
       </c>
       <c r="T82">
-        <v>3.781633299561653</v>
+        <v>3.973881403905398</v>
       </c>
       <c r="U82">
         <v>0.0578</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>4.138755415661073</v>
+        <v>4.087659669788715</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1064284791224527</v>
+        <v>0.1063628641894035</v>
       </c>
       <c r="C83">
-        <v>56.0568983795981</v>
+        <v>54.33250848710534</v>
       </c>
       <c r="D83">
-        <v>165.7808983795981</v>
+        <v>165.9605084871054</v>
       </c>
       <c r="E83">
-        <v>94.62400000000002</v>
+        <v>96.52800000000002</v>
       </c>
       <c r="F83">
-        <v>154.224</v>
+        <v>156.128</v>
       </c>
       <c r="G83">
         <v>44.5</v>
@@ -8093,28 +8093,28 @@
         <v>36.438</v>
       </c>
       <c r="M83">
-        <v>8.914147200000002</v>
+        <v>9.024198400000001</v>
       </c>
       <c r="N83">
-        <v>27.5238528</v>
+        <v>27.4138016</v>
       </c>
       <c r="O83">
-        <v>4.12857792</v>
+        <v>4.11207024</v>
       </c>
       <c r="P83">
-        <v>23.39527488</v>
+        <v>23.30173136</v>
       </c>
       <c r="Q83">
-        <v>23.83227488</v>
+        <v>23.73873136</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.350700942749751</v>
+        <v>0.3670903566077974</v>
       </c>
       <c r="T83">
-        <v>3.973881403905398</v>
+        <v>4.18749040873178</v>
       </c>
       <c r="U83">
         <v>0.0578</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>4.087659669788715</v>
+        <v>4.037810161620559</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1063628641894035</v>
+        <v>0.1087664992563544</v>
       </c>
       <c r="C84">
-        <v>54.33250848710534</v>
+        <v>46.09325874891468</v>
       </c>
       <c r="D84">
-        <v>165.9605084871054</v>
+        <v>159.6252587489147</v>
       </c>
       <c r="E84">
-        <v>96.52800000000002</v>
+        <v>98.43200000000002</v>
       </c>
       <c r="F84">
-        <v>156.128</v>
+        <v>158.032</v>
       </c>
       <c r="G84">
         <v>44.5</v>
@@ -8175,45 +8175,45 @@
         <v>36.438</v>
       </c>
       <c r="M84">
-        <v>9.024198400000001</v>
+        <v>9.687361600000001</v>
       </c>
       <c r="N84">
-        <v>27.4138016</v>
+        <v>26.7506384</v>
       </c>
       <c r="O84">
-        <v>4.11207024</v>
+        <v>4.01259576</v>
       </c>
       <c r="P84">
-        <v>23.30173136</v>
+        <v>22.73804264</v>
       </c>
       <c r="Q84">
-        <v>23.73873136</v>
+        <v>23.17504264</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3670903566077974</v>
+        <v>0.3854079368020847</v>
       </c>
       <c r="T84">
-        <v>4.18749040873178</v>
+        <v>4.426229884714209</v>
       </c>
       <c r="U84">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V84">
         <v>0.15</v>
       </c>
       <c r="W84">
-        <v>0.04913</v>
+        <v>0.052105</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y84">
-        <v>4.037810161620559</v>
+        <v>3.761395672481143</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1087664992563544</v>
+        <v>0.1087306343233052</v>
       </c>
       <c r="C85">
-        <v>46.09325874891468</v>
+        <v>44.28023112317314</v>
       </c>
       <c r="D85">
-        <v>159.6252587489147</v>
+        <v>159.7162311231731</v>
       </c>
       <c r="E85">
-        <v>98.43200000000002</v>
+        <v>100.336</v>
       </c>
       <c r="F85">
-        <v>158.032</v>
+        <v>159.936</v>
       </c>
       <c r="G85">
         <v>44.5</v>
@@ -8257,28 +8257,28 @@
         <v>36.438</v>
       </c>
       <c r="M85">
-        <v>9.687361600000001</v>
+        <v>9.804076800000001</v>
       </c>
       <c r="N85">
-        <v>26.7506384</v>
+        <v>26.6339232</v>
       </c>
       <c r="O85">
-        <v>4.01259576</v>
+        <v>3.99508848</v>
       </c>
       <c r="P85">
-        <v>22.73804264</v>
+        <v>22.63883472</v>
       </c>
       <c r="Q85">
-        <v>23.17504264</v>
+        <v>23.07583472</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3854079368020847</v>
+        <v>0.4060152145206579</v>
       </c>
       <c r="T85">
-        <v>4.426229884714209</v>
+        <v>4.694811795194441</v>
       </c>
       <c r="U85">
         <v>0.0613</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>3.761395672481143</v>
+        <v>3.716617152570653</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1087306343233052</v>
+        <v>0.1086947693902561</v>
       </c>
       <c r="C86">
-        <v>44.28023112317314</v>
+        <v>42.46730724908363</v>
       </c>
       <c r="D86">
-        <v>159.7162311231731</v>
+        <v>159.8073072490836</v>
       </c>
       <c r="E86">
-        <v>100.336</v>
+        <v>102.24</v>
       </c>
       <c r="F86">
-        <v>159.936</v>
+        <v>161.84</v>
       </c>
       <c r="G86">
         <v>44.5</v>
@@ -8339,28 +8339,28 @@
         <v>36.438</v>
       </c>
       <c r="M86">
-        <v>9.804076800000001</v>
+        <v>9.920792</v>
       </c>
       <c r="N86">
-        <v>26.6339232</v>
+        <v>26.517208</v>
       </c>
       <c r="O86">
-        <v>3.99508848</v>
+        <v>3.9775812</v>
       </c>
       <c r="P86">
-        <v>22.63883472</v>
+        <v>22.5396268</v>
       </c>
       <c r="Q86">
-        <v>23.07583472</v>
+        <v>22.97662680000001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4060152145206576</v>
+        <v>0.4293701292683738</v>
       </c>
       <c r="T86">
-        <v>4.694811795194437</v>
+        <v>4.999204627072032</v>
       </c>
       <c r="U86">
         <v>0.0613</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>3.716617152570653</v>
+        <v>3.672892244893351</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1086947693902561</v>
+        <v>0.1086589044572069</v>
       </c>
       <c r="C87">
-        <v>42.46730724908363</v>
+        <v>40.6544873042364</v>
       </c>
       <c r="D87">
-        <v>159.8073072490836</v>
+        <v>159.8984873042364</v>
       </c>
       <c r="E87">
-        <v>102.24</v>
+        <v>104.144</v>
       </c>
       <c r="F87">
-        <v>161.84</v>
+        <v>163.744</v>
       </c>
       <c r="G87">
         <v>44.5</v>
@@ -8421,28 +8421,28 @@
         <v>36.438</v>
       </c>
       <c r="M87">
-        <v>9.920792</v>
+        <v>10.0375072</v>
       </c>
       <c r="N87">
-        <v>26.517208</v>
+        <v>26.4004928</v>
       </c>
       <c r="O87">
-        <v>3.9775812</v>
+        <v>3.96007392</v>
       </c>
       <c r="P87">
-        <v>22.5396268</v>
+        <v>22.44041888</v>
       </c>
       <c r="Q87">
-        <v>22.97662680000001</v>
+        <v>22.87741888</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4293701292683738</v>
+        <v>0.4560614604086208</v>
       </c>
       <c r="T87">
-        <v>4.999204627072032</v>
+        <v>5.347082149217855</v>
       </c>
       <c r="U87">
         <v>0.0613</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>3.672892244893351</v>
+        <v>3.630184195534127</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1086589044572069</v>
+        <v>0.1086230395241577</v>
       </c>
       <c r="C88">
-        <v>40.6544873042364</v>
+        <v>38.84177146662759</v>
       </c>
       <c r="D88">
-        <v>159.8984873042364</v>
+        <v>159.9897714666276</v>
       </c>
       <c r="E88">
-        <v>104.144</v>
+        <v>106.048</v>
       </c>
       <c r="F88">
-        <v>163.744</v>
+        <v>165.648</v>
       </c>
       <c r="G88">
         <v>44.5</v>
@@ -8503,28 +8503,28 @@
         <v>36.438</v>
       </c>
       <c r="M88">
-        <v>10.0375072</v>
+        <v>10.1542224</v>
       </c>
       <c r="N88">
-        <v>26.4004928</v>
+        <v>26.2837776</v>
       </c>
       <c r="O88">
-        <v>3.96007392</v>
+        <v>3.94256664</v>
       </c>
       <c r="P88">
-        <v>22.44041888</v>
+        <v>22.34121096</v>
       </c>
       <c r="Q88">
-        <v>22.87741888</v>
+        <v>22.77821096</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4560614604086208</v>
+        <v>0.4868591501858289</v>
       </c>
       <c r="T88">
-        <v>5.347082149217855</v>
+        <v>5.748479290155343</v>
       </c>
       <c r="U88">
         <v>0.0613</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>3.630184195534127</v>
+        <v>3.588457940413044</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1086230395241577</v>
+        <v>0.1085871745911086</v>
       </c>
       <c r="C89">
-        <v>38.84177146662759</v>
+        <v>37.02915991465963</v>
       </c>
       <c r="D89">
-        <v>159.9897714666276</v>
+        <v>160.0811599146596</v>
       </c>
       <c r="E89">
-        <v>106.048</v>
+        <v>107.952</v>
       </c>
       <c r="F89">
-        <v>165.648</v>
+        <v>167.552</v>
       </c>
       <c r="G89">
         <v>44.5</v>
@@ -8585,28 +8585,28 @@
         <v>36.438</v>
       </c>
       <c r="M89">
-        <v>10.1542224</v>
+        <v>10.2709376</v>
       </c>
       <c r="N89">
-        <v>26.2837776</v>
+        <v>26.1670624</v>
       </c>
       <c r="O89">
-        <v>3.94256664</v>
+        <v>3.92505936</v>
       </c>
       <c r="P89">
-        <v>22.34121096</v>
+        <v>22.24200304</v>
       </c>
       <c r="Q89">
-        <v>22.77821096</v>
+        <v>22.67900304</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4868591501858289</v>
+        <v>0.5227897882592385</v>
       </c>
       <c r="T89">
-        <v>5.748479290155343</v>
+        <v>6.216775954582413</v>
       </c>
       <c r="U89">
         <v>0.0613</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>3.588457940413044</v>
+        <v>3.547680009271987</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1085871745911086</v>
+        <v>0.1085513096580595</v>
       </c>
       <c r="C90">
-        <v>37.02915991465963</v>
+        <v>35.21665282714312</v>
       </c>
       <c r="D90">
-        <v>160.0811599146596</v>
+        <v>160.1726528271431</v>
       </c>
       <c r="E90">
-        <v>107.952</v>
+        <v>109.856</v>
       </c>
       <c r="F90">
-        <v>167.552</v>
+        <v>169.456</v>
       </c>
       <c r="G90">
         <v>44.5</v>
@@ -8667,28 +8667,28 @@
         <v>36.438</v>
       </c>
       <c r="M90">
-        <v>10.2709376</v>
+        <v>10.3876528</v>
       </c>
       <c r="N90">
-        <v>26.1670624</v>
+        <v>26.0503472</v>
       </c>
       <c r="O90">
-        <v>3.92505936</v>
+        <v>3.90755208</v>
       </c>
       <c r="P90">
-        <v>22.24200304</v>
+        <v>22.14279512</v>
       </c>
       <c r="Q90">
-        <v>22.67900304</v>
+        <v>22.57979512</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5227897882592385</v>
+        <v>0.5652532696187224</v>
       </c>
       <c r="T90">
-        <v>6.216775954582413</v>
+        <v>6.770217467087132</v>
       </c>
       <c r="U90">
         <v>0.0613</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>3.547680009271987</v>
+        <v>3.507818436134099</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1085513096580595</v>
+        <v>0.1106574447250103</v>
       </c>
       <c r="C91">
-        <v>35.21665282714312</v>
+        <v>28.11131869632587</v>
       </c>
       <c r="D91">
-        <v>160.1726528271431</v>
+        <v>154.9713186963259</v>
       </c>
       <c r="E91">
-        <v>109.856</v>
+        <v>111.76</v>
       </c>
       <c r="F91">
-        <v>169.456</v>
+        <v>171.36</v>
       </c>
       <c r="G91">
         <v>44.5</v>
@@ -8749,45 +8749,45 @@
         <v>36.438</v>
       </c>
       <c r="M91">
-        <v>10.3876528</v>
+        <v>10.984176</v>
       </c>
       <c r="N91">
-        <v>26.0503472</v>
+        <v>25.453824</v>
       </c>
       <c r="O91">
-        <v>3.90755208</v>
+        <v>3.8180736</v>
       </c>
       <c r="P91">
-        <v>22.14279512</v>
+        <v>21.6357504</v>
       </c>
       <c r="Q91">
-        <v>22.57979512</v>
+        <v>22.0727504</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5652532696187224</v>
+        <v>0.6162094472501033</v>
       </c>
       <c r="T91">
-        <v>6.770217467087132</v>
+        <v>7.434347282092796</v>
       </c>
       <c r="U91">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V91">
         <v>0.15</v>
       </c>
       <c r="W91">
-        <v>0.052105</v>
+        <v>0.054485</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y91">
-        <v>3.507818436134099</v>
+        <v>3.317317566652246</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1106574447250103</v>
+        <v>0.1106453797919612</v>
       </c>
       <c r="C92">
-        <v>28.11131869632587</v>
+        <v>26.23615218593775</v>
       </c>
       <c r="D92">
-        <v>154.9713186963259</v>
+        <v>155.0001521859378</v>
       </c>
       <c r="E92">
-        <v>111.76</v>
+        <v>113.664</v>
       </c>
       <c r="F92">
-        <v>171.36</v>
+        <v>173.264</v>
       </c>
       <c r="G92">
         <v>44.5</v>
@@ -8831,28 +8831,28 @@
         <v>36.438</v>
       </c>
       <c r="M92">
-        <v>10.984176</v>
+        <v>11.1062224</v>
       </c>
       <c r="N92">
-        <v>25.453824</v>
+        <v>25.3317776</v>
       </c>
       <c r="O92">
-        <v>3.8180736</v>
+        <v>3.79976664</v>
       </c>
       <c r="P92">
-        <v>21.6357504</v>
+        <v>21.53201096</v>
       </c>
       <c r="Q92">
-        <v>22.0727504</v>
+        <v>21.96901096</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6162094472501033</v>
+        <v>0.6784892199106797</v>
       </c>
       <c r="T92">
-        <v>7.434347282092796</v>
+        <v>8.246061500433049</v>
       </c>
       <c r="U92">
         <v>0.0641</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>3.317317566652246</v>
+        <v>3.280863527458265</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1106453797919612</v>
+        <v>0.110633314858912</v>
       </c>
       <c r="C93">
-        <v>26.23615218593775</v>
+        <v>24.36099640688803</v>
       </c>
       <c r="D93">
-        <v>155.0001521859378</v>
+        <v>155.028996406888</v>
       </c>
       <c r="E93">
-        <v>113.664</v>
+        <v>115.568</v>
       </c>
       <c r="F93">
-        <v>173.264</v>
+        <v>175.168</v>
       </c>
       <c r="G93">
         <v>44.5</v>
@@ -8913,28 +8913,28 @@
         <v>36.438</v>
       </c>
       <c r="M93">
-        <v>11.1062224</v>
+        <v>11.2282688</v>
       </c>
       <c r="N93">
-        <v>25.3317776</v>
+        <v>25.2097312</v>
       </c>
       <c r="O93">
-        <v>3.79976664</v>
+        <v>3.78145968</v>
       </c>
       <c r="P93">
-        <v>21.53201096</v>
+        <v>21.42827152</v>
       </c>
       <c r="Q93">
-        <v>21.96901096</v>
+        <v>21.86527152</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6784892199106797</v>
+        <v>0.7563389357364004</v>
       </c>
       <c r="T93">
-        <v>8.246061500433049</v>
+        <v>9.260704273358369</v>
       </c>
       <c r="U93">
         <v>0.0641</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>3.280863527458265</v>
+        <v>3.245201967377197</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.110633314858912</v>
+        <v>0.1106212499258628</v>
       </c>
       <c r="C94">
-        <v>24.36099640688803</v>
+        <v>22.48585136516897</v>
       </c>
       <c r="D94">
-        <v>155.028996406888</v>
+        <v>155.057851365169</v>
       </c>
       <c r="E94">
-        <v>115.568</v>
+        <v>117.472</v>
       </c>
       <c r="F94">
-        <v>175.168</v>
+        <v>177.072</v>
       </c>
       <c r="G94">
         <v>44.5</v>
@@ -8995,28 +8995,28 @@
         <v>36.438</v>
       </c>
       <c r="M94">
-        <v>11.2282688</v>
+        <v>11.3503152</v>
       </c>
       <c r="N94">
-        <v>25.2097312</v>
+        <v>25.0876848</v>
       </c>
       <c r="O94">
-        <v>3.78145968</v>
+        <v>3.76315272</v>
       </c>
       <c r="P94">
-        <v>21.42827152</v>
+        <v>21.32453208</v>
       </c>
       <c r="Q94">
-        <v>21.86527152</v>
+        <v>21.76153208</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7563389357364004</v>
+        <v>0.856431427512327</v>
       </c>
       <c r="T94">
-        <v>9.260704273358369</v>
+        <v>10.56524498140521</v>
       </c>
       <c r="U94">
         <v>0.0641</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>3.245201967377197</v>
+        <v>3.21030732256669</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1106212499258628</v>
+        <v>0.1106091849928137</v>
       </c>
       <c r="C95">
-        <v>22.48585136516897</v>
+        <v>20.61071706677703</v>
       </c>
       <c r="D95">
-        <v>155.057851365169</v>
+        <v>155.0867170667771</v>
       </c>
       <c r="E95">
-        <v>117.472</v>
+        <v>119.376</v>
       </c>
       <c r="F95">
-        <v>177.072</v>
+        <v>178.976</v>
       </c>
       <c r="G95">
         <v>44.5</v>
@@ -9077,28 +9077,28 @@
         <v>36.438</v>
       </c>
       <c r="M95">
-        <v>11.3503152</v>
+        <v>11.4723616</v>
       </c>
       <c r="N95">
-        <v>25.0876848</v>
+        <v>24.9656384</v>
       </c>
       <c r="O95">
-        <v>3.76315272</v>
+        <v>3.74484576</v>
       </c>
       <c r="P95">
-        <v>21.32453208</v>
+        <v>21.22079264</v>
       </c>
       <c r="Q95">
-        <v>21.76153208</v>
+        <v>21.65779264</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.856431427512327</v>
+        <v>0.9898880832135627</v>
       </c>
       <c r="T95">
-        <v>10.56524498140521</v>
+        <v>12.30463259213433</v>
       </c>
       <c r="U95">
         <v>0.0641</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>3.21030732256669</v>
+        <v>3.176155117007469</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1106091849928137</v>
+        <v>0.1105971200597646</v>
       </c>
       <c r="C96">
-        <v>20.61071706677703</v>
+        <v>18.73559351771334</v>
       </c>
       <c r="D96">
-        <v>155.0867170667771</v>
+        <v>155.1155935177134</v>
       </c>
       <c r="E96">
-        <v>119.376</v>
+        <v>121.28</v>
       </c>
       <c r="F96">
-        <v>178.976</v>
+        <v>180.88</v>
       </c>
       <c r="G96">
         <v>44.5</v>
@@ -9159,28 +9159,28 @@
         <v>36.438</v>
       </c>
       <c r="M96">
-        <v>11.4723616</v>
+        <v>11.594408</v>
       </c>
       <c r="N96">
-        <v>24.9656384</v>
+        <v>24.843592</v>
       </c>
       <c r="O96">
-        <v>3.74484576</v>
+        <v>3.7265388</v>
       </c>
       <c r="P96">
-        <v>21.22079264</v>
+        <v>21.1170532</v>
       </c>
       <c r="Q96">
-        <v>21.65779264</v>
+        <v>21.5540532</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9898880832135627</v>
+        <v>1.176727401195293</v>
       </c>
       <c r="T96">
-        <v>12.30463259213433</v>
+        <v>14.7397752471551</v>
       </c>
       <c r="U96">
         <v>0.0641</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>3.176155117007469</v>
+        <v>3.142721905249496</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1105971200597646</v>
+        <v>0.1105850551267154</v>
       </c>
       <c r="C97">
-        <v>18.73559351771334</v>
+        <v>16.86048072398356</v>
       </c>
       <c r="D97">
-        <v>155.1155935177134</v>
+        <v>155.1444807239836</v>
       </c>
       <c r="E97">
-        <v>121.28</v>
+        <v>123.184</v>
       </c>
       <c r="F97">
-        <v>180.88</v>
+        <v>182.784</v>
       </c>
       <c r="G97">
         <v>44.5</v>
@@ -9241,28 +9241,28 @@
         <v>36.438</v>
       </c>
       <c r="M97">
-        <v>11.594408</v>
+        <v>11.7164544</v>
       </c>
       <c r="N97">
-        <v>24.843592</v>
+        <v>24.7215456</v>
       </c>
       <c r="O97">
-        <v>3.7265388</v>
+        <v>3.70823184</v>
       </c>
       <c r="P97">
-        <v>21.1170532</v>
+        <v>21.01331376</v>
       </c>
       <c r="Q97">
-        <v>21.5540532</v>
+        <v>21.45031376</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.176727401195293</v>
+        <v>1.456986378167888</v>
       </c>
       <c r="T97">
-        <v>14.7397752471551</v>
+        <v>18.39248922968625</v>
       </c>
       <c r="U97">
         <v>0.0641</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>3.142721905249496</v>
+        <v>3.10998521873648</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1105850551267154</v>
+        <v>0.1105729901936663</v>
       </c>
       <c r="C98">
-        <v>16.86048072398358</v>
+        <v>14.98537869159759</v>
       </c>
       <c r="D98">
-        <v>155.1444807239836</v>
+        <v>155.1733786915976</v>
       </c>
       <c r="E98">
-        <v>123.184</v>
+        <v>125.088</v>
       </c>
       <c r="F98">
-        <v>182.784</v>
+        <v>184.688</v>
       </c>
       <c r="G98">
         <v>44.5</v>
@@ -9323,28 +9323,28 @@
         <v>36.438</v>
       </c>
       <c r="M98">
-        <v>11.7164544</v>
+        <v>11.8385008</v>
       </c>
       <c r="N98">
-        <v>24.7215456</v>
+        <v>24.5994992</v>
       </c>
       <c r="O98">
-        <v>3.70823184</v>
+        <v>3.68992488</v>
       </c>
       <c r="P98">
-        <v>21.01331376</v>
+        <v>20.90957432</v>
       </c>
       <c r="Q98">
-        <v>21.45031376</v>
+        <v>21.34657432000001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.456986378167884</v>
+        <v>1.924084673122207</v>
       </c>
       <c r="T98">
-        <v>18.3924892296862</v>
+        <v>24.4803458672381</v>
       </c>
       <c r="U98">
         <v>0.0641</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>3.109985218736481</v>
+        <v>3.077923515450538</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1105729901936663</v>
+        <v>0.1105609252606171</v>
       </c>
       <c r="C99">
-        <v>14.98537869159759</v>
+        <v>13.11028742656993</v>
       </c>
       <c r="D99">
-        <v>155.1733786915976</v>
+        <v>155.2022874265699</v>
       </c>
       <c r="E99">
-        <v>125.088</v>
+        <v>126.992</v>
       </c>
       <c r="F99">
-        <v>184.688</v>
+        <v>186.592</v>
       </c>
       <c r="G99">
         <v>44.5</v>
@@ -9405,28 +9405,28 @@
         <v>36.438</v>
       </c>
       <c r="M99">
-        <v>11.8385008</v>
+        <v>11.9605472</v>
       </c>
       <c r="N99">
-        <v>24.5994992</v>
+        <v>24.4774528</v>
       </c>
       <c r="O99">
-        <v>3.68992488</v>
+        <v>3.67161792</v>
       </c>
       <c r="P99">
-        <v>20.90957432</v>
+        <v>20.80583488</v>
       </c>
       <c r="Q99">
-        <v>21.34657432000001</v>
+        <v>21.24283488</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.924084673122207</v>
+        <v>2.858281263030853</v>
       </c>
       <c r="T99">
-        <v>24.4803458672381</v>
+        <v>36.6560591423419</v>
       </c>
       <c r="U99">
         <v>0.0641</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>3.077923515450538</v>
+        <v>3.046516132639817</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1105609252606171</v>
+        <v>0.1105488603275679</v>
       </c>
       <c r="C100">
-        <v>13.11028742656993</v>
+        <v>11.23520693491969</v>
       </c>
       <c r="D100">
-        <v>155.2022874265699</v>
+        <v>155.2312069349197</v>
       </c>
       <c r="E100">
-        <v>126.992</v>
+        <v>128.896</v>
       </c>
       <c r="F100">
-        <v>186.592</v>
+        <v>188.496</v>
       </c>
       <c r="G100">
         <v>44.5</v>
@@ -9487,28 +9487,28 @@
         <v>36.438</v>
       </c>
       <c r="M100">
-        <v>11.9605472</v>
+        <v>12.0825936</v>
       </c>
       <c r="N100">
-        <v>24.4774528</v>
+        <v>24.3554064</v>
       </c>
       <c r="O100">
-        <v>3.67161792</v>
+        <v>3.65331096</v>
       </c>
       <c r="P100">
-        <v>20.80583488</v>
+        <v>20.70209544</v>
       </c>
       <c r="Q100">
-        <v>21.24283488</v>
+        <v>21.13909544</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.858281263030853</v>
+        <v>5.66087103275679</v>
       </c>
       <c r="T100">
-        <v>36.6560591423419</v>
+        <v>73.18319896765327</v>
       </c>
       <c r="U100">
         <v>0.0641</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>3.046516132639817</v>
+        <v>3.015743242411133</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1105488603275679</v>
-      </c>
-      <c r="C101">
-        <v>11.23520693491969</v>
-      </c>
-      <c r="D101">
-        <v>155.2312069349197</v>
-      </c>
-      <c r="E101">
-        <v>128.896</v>
-      </c>
-      <c r="F101">
-        <v>188.496</v>
-      </c>
-      <c r="G101">
-        <v>44.5</v>
-      </c>
-      <c r="H101">
-        <v>130.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>36.875</v>
-      </c>
-      <c r="K101">
-        <v>0.437</v>
-      </c>
-      <c r="L101">
-        <v>36.438</v>
-      </c>
-      <c r="M101">
-        <v>12.0825936</v>
-      </c>
-      <c r="N101">
-        <v>24.3554064</v>
-      </c>
-      <c r="O101">
-        <v>3.65331096</v>
-      </c>
-      <c r="P101">
-        <v>20.70209544</v>
-      </c>
-      <c r="Q101">
-        <v>21.13909544</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.66087103275679</v>
-      </c>
-      <c r="T101">
-        <v>73.18319896765327</v>
-      </c>
-      <c r="U101">
-        <v>0.0641</v>
-      </c>
-      <c r="V101">
-        <v>0.15</v>
-      </c>
-      <c r="W101">
-        <v>0.054485</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ba2/BB</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>3.015743242411133</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
